--- a/Data/merged_data.xlsx
+++ b/Data/merged_data.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>M1_1.4</t>
+          <t>M1_1.4_EOU</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>M1_1.5</t>
+          <t>M1_1.5_effort</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>M1_2.5</t>
+          <t>M1_2.5_EOU</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>M1_2.6</t>
+          <t>M1_2.6_effort</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>M1_3.6</t>
+          <t>M1_3.6_EOU</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>M1_3.7</t>
+          <t>M1_3.7_effort</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>M1_4.5</t>
+          <t>M1_4.5_EOU</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>M1_4.6</t>
+          <t>M1_4.6_effort</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>M1_5.3</t>
+          <t>M1_5.3_EOU</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>M1_5.4</t>
+          <t>M1_5.4_effort</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>M1_6.3</t>
+          <t>M1_6.3_EOU</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>M1_6.4</t>
+          <t>M1_6.4_effort</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>M2_1.4</t>
+          <t>M2_1.4_EOU</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>M2_1.5</t>
+          <t>M2_1.5_effort</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>M2_2.5</t>
+          <t>M2_2.5_EOU</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>M2_2.6</t>
+          <t>M2_2.6_effort</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
-          <t>M2_3.6</t>
+          <t>M2_3.6_EOU</t>
         </is>
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>M2_3.7</t>
+          <t>M2_3.7_effort</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>M2_4.5</t>
+          <t>M2_4.5_EOU</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>M2_4.6</t>
+          <t>M2_4.6_effort</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>M2_5.3</t>
+          <t>M2_5.3_EOU</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
-          <t>M2_5.4</t>
+          <t>M2_5.4_effort</t>
         </is>
       </c>
       <c r="DU1" s="1" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
-          <t>M2_6.3</t>
+          <t>M2_6.3_EOU</t>
         </is>
       </c>
       <c r="DZ1" s="1" t="inlineStr">
         <is>
-          <t>M2_6.4</t>
+          <t>M2_6.4_effort</t>
         </is>
       </c>
       <c r="EA1" s="1" t="inlineStr">
@@ -4023,143 +4023,411 @@
           <t>A</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11.04.1940</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Stroke</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Metabolic syndrome</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>54.5kg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>few days</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>28</v>
+      </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
-      <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
-      <c r="CE9" t="inlineStr"/>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr"/>
-      <c r="CH9" t="inlineStr"/>
-      <c r="CI9" t="inlineStr"/>
-      <c r="CJ9" t="inlineStr"/>
-      <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="inlineStr"/>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="inlineStr"/>
-      <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="inlineStr"/>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="inlineStr"/>
-      <c r="DD9" t="inlineStr"/>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
-      <c r="DG9" t="inlineStr"/>
-      <c r="DH9" t="inlineStr"/>
-      <c r="DI9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>30</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>193</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>187</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>134</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>133</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>73</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>45</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>27</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>6</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>6</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>30</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>7</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>54</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>174</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>128</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>140</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>5</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>9</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
       <c r="DJ9" t="inlineStr"/>
-      <c r="DK9" t="inlineStr"/>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
       <c r="DL9" t="inlineStr"/>
-      <c r="DM9" t="inlineStr"/>
-      <c r="DN9" t="inlineStr"/>
-      <c r="DO9" t="inlineStr"/>
+      <c r="DM9" t="n">
+        <v>6</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>6</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0</v>
+      </c>
       <c r="DP9" t="inlineStr"/>
-      <c r="DQ9" t="inlineStr"/>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
       <c r="DR9" t="inlineStr"/>
       <c r="DS9" t="inlineStr"/>
       <c r="DT9" t="inlineStr"/>
-      <c r="DU9" t="inlineStr"/>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
       <c r="DV9" t="inlineStr"/>
-      <c r="DW9" t="inlineStr"/>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
       <c r="DX9" t="inlineStr"/>
       <c r="DY9" t="inlineStr"/>
       <c r="DZ9" t="inlineStr"/>
-      <c r="EA9" t="inlineStr"/>
-      <c r="EB9" t="inlineStr"/>
-      <c r="EC9" t="inlineStr"/>
-      <c r="ED9" t="inlineStr"/>
-      <c r="EE9" t="inlineStr"/>
-      <c r="EF9" t="inlineStr"/>
-      <c r="EG9" t="inlineStr"/>
-      <c r="EH9" t="inlineStr"/>
-      <c r="EI9" t="inlineStr"/>
+      <c r="EA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>5</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>2.077</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/Data/merged_data.xlsx
+++ b/Data/merged_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI23"/>
+  <dimension ref="A1:EI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4435,151 +4435,419 @@
           <t>P09</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>09.08.1957</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Arthritis</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60kg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>29</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>28</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>146</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>331</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>142</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
       <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
       <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
       <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
       <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
       <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr"/>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
-      <c r="BZ10" t="inlineStr"/>
-      <c r="CA10" t="inlineStr"/>
-      <c r="CB10" t="inlineStr"/>
-      <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr"/>
-      <c r="CE10" t="inlineStr"/>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr"/>
-      <c r="CH10" t="inlineStr"/>
-      <c r="CI10" t="inlineStr"/>
-      <c r="CJ10" t="inlineStr"/>
-      <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="inlineStr"/>
-      <c r="CZ10" t="inlineStr"/>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="inlineStr"/>
-      <c r="DD10" t="inlineStr"/>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="inlineStr"/>
-      <c r="DK10" t="inlineStr"/>
-      <c r="DL10" t="inlineStr"/>
-      <c r="DM10" t="inlineStr"/>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr"/>
-      <c r="DP10" t="inlineStr"/>
-      <c r="DQ10" t="inlineStr"/>
-      <c r="DR10" t="inlineStr"/>
-      <c r="DS10" t="inlineStr"/>
-      <c r="DT10" t="inlineStr"/>
-      <c r="DU10" t="inlineStr"/>
-      <c r="DV10" t="inlineStr"/>
-      <c r="DW10" t="inlineStr"/>
-      <c r="DX10" t="inlineStr"/>
-      <c r="DY10" t="inlineStr"/>
-      <c r="DZ10" t="inlineStr"/>
-      <c r="EA10" t="inlineStr"/>
-      <c r="EB10" t="inlineStr"/>
-      <c r="EC10" t="inlineStr"/>
-      <c r="ED10" t="inlineStr"/>
-      <c r="EE10" t="inlineStr"/>
-      <c r="EF10" t="inlineStr"/>
-      <c r="EG10" t="inlineStr"/>
-      <c r="EH10" t="inlineStr"/>
-      <c r="EI10" t="inlineStr"/>
+      <c r="BR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>57</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>86</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>6</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>7</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>39</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>31</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>31</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>212</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>42</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>42</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>270</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>123</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>16</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>16</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>150</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>110</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>62</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>48</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>155</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>82</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>3</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4720,11 +4988,7 @@
       <c r="EI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4867,7 +5131,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -5012,7 +5276,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -5157,7 +5421,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -5302,7 +5566,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -5447,7 +5711,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -5592,7 +5856,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -5737,7 +6001,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -5882,7 +6146,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -6027,7 +6291,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -6172,7 +6436,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -6317,7 +6581,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -6459,6 +6723,296 @@
       <c r="EH23" t="inlineStr"/>
       <c r="EI23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr"/>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
+      <c r="DD24" t="inlineStr"/>
+      <c r="DE24" t="inlineStr"/>
+      <c r="DF24" t="inlineStr"/>
+      <c r="DG24" t="inlineStr"/>
+      <c r="DH24" t="inlineStr"/>
+      <c r="DI24" t="inlineStr"/>
+      <c r="DJ24" t="inlineStr"/>
+      <c r="DK24" t="inlineStr"/>
+      <c r="DL24" t="inlineStr"/>
+      <c r="DM24" t="inlineStr"/>
+      <c r="DN24" t="inlineStr"/>
+      <c r="DO24" t="inlineStr"/>
+      <c r="DP24" t="inlineStr"/>
+      <c r="DQ24" t="inlineStr"/>
+      <c r="DR24" t="inlineStr"/>
+      <c r="DS24" t="inlineStr"/>
+      <c r="DT24" t="inlineStr"/>
+      <c r="DU24" t="inlineStr"/>
+      <c r="DV24" t="inlineStr"/>
+      <c r="DW24" t="inlineStr"/>
+      <c r="DX24" t="inlineStr"/>
+      <c r="DY24" t="inlineStr"/>
+      <c r="DZ24" t="inlineStr"/>
+      <c r="EA24" t="inlineStr"/>
+      <c r="EB24" t="inlineStr"/>
+      <c r="EC24" t="inlineStr"/>
+      <c r="ED24" t="inlineStr"/>
+      <c r="EE24" t="inlineStr"/>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr"/>
+      <c r="EH24" t="inlineStr"/>
+      <c r="EI24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="inlineStr"/>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="inlineStr"/>
+      <c r="CK25" t="inlineStr"/>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr"/>
+      <c r="CY25" t="inlineStr"/>
+      <c r="CZ25" t="inlineStr"/>
+      <c r="DA25" t="inlineStr"/>
+      <c r="DB25" t="inlineStr"/>
+      <c r="DC25" t="inlineStr"/>
+      <c r="DD25" t="inlineStr"/>
+      <c r="DE25" t="inlineStr"/>
+      <c r="DF25" t="inlineStr"/>
+      <c r="DG25" t="inlineStr"/>
+      <c r="DH25" t="inlineStr"/>
+      <c r="DI25" t="inlineStr"/>
+      <c r="DJ25" t="inlineStr"/>
+      <c r="DK25" t="inlineStr"/>
+      <c r="DL25" t="inlineStr"/>
+      <c r="DM25" t="inlineStr"/>
+      <c r="DN25" t="inlineStr"/>
+      <c r="DO25" t="inlineStr"/>
+      <c r="DP25" t="inlineStr"/>
+      <c r="DQ25" t="inlineStr"/>
+      <c r="DR25" t="inlineStr"/>
+      <c r="DS25" t="inlineStr"/>
+      <c r="DT25" t="inlineStr"/>
+      <c r="DU25" t="inlineStr"/>
+      <c r="DV25" t="inlineStr"/>
+      <c r="DW25" t="inlineStr"/>
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr"/>
+      <c r="DZ25" t="inlineStr"/>
+      <c r="EA25" t="inlineStr"/>
+      <c r="EB25" t="inlineStr"/>
+      <c r="EC25" t="inlineStr"/>
+      <c r="ED25" t="inlineStr"/>
+      <c r="EE25" t="inlineStr"/>
+      <c r="EF25" t="inlineStr"/>
+      <c r="EG25" t="inlineStr"/>
+      <c r="EH25" t="inlineStr"/>
+      <c r="EI25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/merged_data.xlsx
+++ b/Data/merged_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI25"/>
+  <dimension ref="A1:EI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>manual wheelchair since a few montha</t>
+          <t>manual wheelchair since a few months</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4847,7 +4847,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4988,7 +4992,11 @@
       <c r="EI11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -5131,152 +5139,428 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>09.07.1985</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>University Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>60kg</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>few weeks</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>30</v>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
-      <c r="BW13" t="inlineStr"/>
-      <c r="BX13" t="inlineStr"/>
-      <c r="BY13" t="inlineStr"/>
-      <c r="BZ13" t="inlineStr"/>
-      <c r="CA13" t="inlineStr"/>
-      <c r="CB13" t="inlineStr"/>
-      <c r="CC13" t="inlineStr"/>
-      <c r="CD13" t="inlineStr"/>
-      <c r="CE13" t="inlineStr"/>
-      <c r="CF13" t="inlineStr"/>
-      <c r="CG13" t="inlineStr"/>
-      <c r="CH13" t="inlineStr"/>
-      <c r="CI13" t="inlineStr"/>
-      <c r="CJ13" t="inlineStr"/>
-      <c r="CK13" t="inlineStr"/>
-      <c r="CL13" t="inlineStr"/>
-      <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="inlineStr"/>
-      <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="inlineStr"/>
-      <c r="DI13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>15</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>31</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>261</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>123</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>212</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>86</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>83</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>113</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>84</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>13</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>7</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>7</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>25</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>20</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>9</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>24</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>75</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>75</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>102</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>6</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>12</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0</v>
+      </c>
       <c r="DJ13" t="inlineStr"/>
-      <c r="DK13" t="inlineStr"/>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
       <c r="DL13" t="inlineStr"/>
-      <c r="DM13" t="inlineStr"/>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="inlineStr"/>
+      <c r="DM13" t="n">
+        <v>5</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0</v>
+      </c>
       <c r="DP13" t="inlineStr"/>
-      <c r="DQ13" t="inlineStr"/>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
       <c r="DR13" t="inlineStr"/>
       <c r="DS13" t="inlineStr"/>
       <c r="DT13" t="inlineStr"/>
-      <c r="DU13" t="inlineStr"/>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
       <c r="DV13" t="inlineStr"/>
-      <c r="DW13" t="inlineStr"/>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
       <c r="DX13" t="inlineStr"/>
       <c r="DY13" t="inlineStr"/>
       <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="inlineStr"/>
-      <c r="EB13" t="inlineStr"/>
-      <c r="EC13" t="inlineStr"/>
-      <c r="ED13" t="inlineStr"/>
-      <c r="EE13" t="inlineStr"/>
-      <c r="EF13" t="inlineStr"/>
-      <c r="EG13" t="inlineStr"/>
-      <c r="EH13" t="inlineStr"/>
-      <c r="EI13" t="inlineStr"/>
+      <c r="EA13" t="n">
+        <v>6</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -5421,7 +5705,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -5566,7 +5850,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -5711,7 +5995,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -5856,7 +6140,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -6001,7 +6285,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -6146,7 +6430,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -6291,7 +6575,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -6436,7 +6720,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -6581,7 +6865,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -6723,296 +7007,6 @@
       <c r="EH23" t="inlineStr"/>
       <c r="EI23" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
-      <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
-      <c r="BF24" t="inlineStr"/>
-      <c r="BG24" t="inlineStr"/>
-      <c r="BH24" t="inlineStr"/>
-      <c r="BI24" t="inlineStr"/>
-      <c r="BJ24" t="inlineStr"/>
-      <c r="BK24" t="inlineStr"/>
-      <c r="BL24" t="inlineStr"/>
-      <c r="BM24" t="inlineStr"/>
-      <c r="BN24" t="inlineStr"/>
-      <c r="BO24" t="inlineStr"/>
-      <c r="BP24" t="inlineStr"/>
-      <c r="BQ24" t="inlineStr"/>
-      <c r="BR24" t="inlineStr"/>
-      <c r="BS24" t="inlineStr"/>
-      <c r="BT24" t="inlineStr"/>
-      <c r="BU24" t="inlineStr"/>
-      <c r="BV24" t="inlineStr"/>
-      <c r="BW24" t="inlineStr"/>
-      <c r="BX24" t="inlineStr"/>
-      <c r="BY24" t="inlineStr"/>
-      <c r="BZ24" t="inlineStr"/>
-      <c r="CA24" t="inlineStr"/>
-      <c r="CB24" t="inlineStr"/>
-      <c r="CC24" t="inlineStr"/>
-      <c r="CD24" t="inlineStr"/>
-      <c r="CE24" t="inlineStr"/>
-      <c r="CF24" t="inlineStr"/>
-      <c r="CG24" t="inlineStr"/>
-      <c r="CH24" t="inlineStr"/>
-      <c r="CI24" t="inlineStr"/>
-      <c r="CJ24" t="inlineStr"/>
-      <c r="CK24" t="inlineStr"/>
-      <c r="CL24" t="inlineStr"/>
-      <c r="CM24" t="inlineStr"/>
-      <c r="CN24" t="inlineStr"/>
-      <c r="CO24" t="inlineStr"/>
-      <c r="CP24" t="inlineStr"/>
-      <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr"/>
-      <c r="CS24" t="inlineStr"/>
-      <c r="CT24" t="inlineStr"/>
-      <c r="CU24" t="inlineStr"/>
-      <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr"/>
-      <c r="CX24" t="inlineStr"/>
-      <c r="CY24" t="inlineStr"/>
-      <c r="CZ24" t="inlineStr"/>
-      <c r="DA24" t="inlineStr"/>
-      <c r="DB24" t="inlineStr"/>
-      <c r="DC24" t="inlineStr"/>
-      <c r="DD24" t="inlineStr"/>
-      <c r="DE24" t="inlineStr"/>
-      <c r="DF24" t="inlineStr"/>
-      <c r="DG24" t="inlineStr"/>
-      <c r="DH24" t="inlineStr"/>
-      <c r="DI24" t="inlineStr"/>
-      <c r="DJ24" t="inlineStr"/>
-      <c r="DK24" t="inlineStr"/>
-      <c r="DL24" t="inlineStr"/>
-      <c r="DM24" t="inlineStr"/>
-      <c r="DN24" t="inlineStr"/>
-      <c r="DO24" t="inlineStr"/>
-      <c r="DP24" t="inlineStr"/>
-      <c r="DQ24" t="inlineStr"/>
-      <c r="DR24" t="inlineStr"/>
-      <c r="DS24" t="inlineStr"/>
-      <c r="DT24" t="inlineStr"/>
-      <c r="DU24" t="inlineStr"/>
-      <c r="DV24" t="inlineStr"/>
-      <c r="DW24" t="inlineStr"/>
-      <c r="DX24" t="inlineStr"/>
-      <c r="DY24" t="inlineStr"/>
-      <c r="DZ24" t="inlineStr"/>
-      <c r="EA24" t="inlineStr"/>
-      <c r="EB24" t="inlineStr"/>
-      <c r="EC24" t="inlineStr"/>
-      <c r="ED24" t="inlineStr"/>
-      <c r="EE24" t="inlineStr"/>
-      <c r="EF24" t="inlineStr"/>
-      <c r="EG24" t="inlineStr"/>
-      <c r="EH24" t="inlineStr"/>
-      <c r="EI24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
-      <c r="BB25" t="inlineStr"/>
-      <c r="BC25" t="inlineStr"/>
-      <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="inlineStr"/>
-      <c r="BF25" t="inlineStr"/>
-      <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="inlineStr"/>
-      <c r="BI25" t="inlineStr"/>
-      <c r="BJ25" t="inlineStr"/>
-      <c r="BK25" t="inlineStr"/>
-      <c r="BL25" t="inlineStr"/>
-      <c r="BM25" t="inlineStr"/>
-      <c r="BN25" t="inlineStr"/>
-      <c r="BO25" t="inlineStr"/>
-      <c r="BP25" t="inlineStr"/>
-      <c r="BQ25" t="inlineStr"/>
-      <c r="BR25" t="inlineStr"/>
-      <c r="BS25" t="inlineStr"/>
-      <c r="BT25" t="inlineStr"/>
-      <c r="BU25" t="inlineStr"/>
-      <c r="BV25" t="inlineStr"/>
-      <c r="BW25" t="inlineStr"/>
-      <c r="BX25" t="inlineStr"/>
-      <c r="BY25" t="inlineStr"/>
-      <c r="BZ25" t="inlineStr"/>
-      <c r="CA25" t="inlineStr"/>
-      <c r="CB25" t="inlineStr"/>
-      <c r="CC25" t="inlineStr"/>
-      <c r="CD25" t="inlineStr"/>
-      <c r="CE25" t="inlineStr"/>
-      <c r="CF25" t="inlineStr"/>
-      <c r="CG25" t="inlineStr"/>
-      <c r="CH25" t="inlineStr"/>
-      <c r="CI25" t="inlineStr"/>
-      <c r="CJ25" t="inlineStr"/>
-      <c r="CK25" t="inlineStr"/>
-      <c r="CL25" t="inlineStr"/>
-      <c r="CM25" t="inlineStr"/>
-      <c r="CN25" t="inlineStr"/>
-      <c r="CO25" t="inlineStr"/>
-      <c r="CP25" t="inlineStr"/>
-      <c r="CQ25" t="inlineStr"/>
-      <c r="CR25" t="inlineStr"/>
-      <c r="CS25" t="inlineStr"/>
-      <c r="CT25" t="inlineStr"/>
-      <c r="CU25" t="inlineStr"/>
-      <c r="CV25" t="inlineStr"/>
-      <c r="CW25" t="inlineStr"/>
-      <c r="CX25" t="inlineStr"/>
-      <c r="CY25" t="inlineStr"/>
-      <c r="CZ25" t="inlineStr"/>
-      <c r="DA25" t="inlineStr"/>
-      <c r="DB25" t="inlineStr"/>
-      <c r="DC25" t="inlineStr"/>
-      <c r="DD25" t="inlineStr"/>
-      <c r="DE25" t="inlineStr"/>
-      <c r="DF25" t="inlineStr"/>
-      <c r="DG25" t="inlineStr"/>
-      <c r="DH25" t="inlineStr"/>
-      <c r="DI25" t="inlineStr"/>
-      <c r="DJ25" t="inlineStr"/>
-      <c r="DK25" t="inlineStr"/>
-      <c r="DL25" t="inlineStr"/>
-      <c r="DM25" t="inlineStr"/>
-      <c r="DN25" t="inlineStr"/>
-      <c r="DO25" t="inlineStr"/>
-      <c r="DP25" t="inlineStr"/>
-      <c r="DQ25" t="inlineStr"/>
-      <c r="DR25" t="inlineStr"/>
-      <c r="DS25" t="inlineStr"/>
-      <c r="DT25" t="inlineStr"/>
-      <c r="DU25" t="inlineStr"/>
-      <c r="DV25" t="inlineStr"/>
-      <c r="DW25" t="inlineStr"/>
-      <c r="DX25" t="inlineStr"/>
-      <c r="DY25" t="inlineStr"/>
-      <c r="DZ25" t="inlineStr"/>
-      <c r="EA25" t="inlineStr"/>
-      <c r="EB25" t="inlineStr"/>
-      <c r="EC25" t="inlineStr"/>
-      <c r="ED25" t="inlineStr"/>
-      <c r="EE25" t="inlineStr"/>
-      <c r="EF25" t="inlineStr"/>
-      <c r="EG25" t="inlineStr"/>
-      <c r="EH25" t="inlineStr"/>
-      <c r="EI25" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/merged_data.xlsx
+++ b/Data/merged_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI23"/>
+  <dimension ref="A1:EK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,640 +486,650 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>LBI_ATWWH</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LBI_ATWI</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>P.manual_exp</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>P.electric_exp</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>P.MMSE</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>R.FIM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>R.EDSS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>R.others</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>M1_1.1_score</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>M1_1.1_time</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>M1_1.2_score</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>M1_1.2_time</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>M1_1.3_score</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>M1_1.3_time</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>M1_1.4_EOU</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>M1_1.5_effort</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>M1_2.1_score</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>M1_2.1_time</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>M1_2.2_score</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>M1_2.2_time</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>M1_2.3_score</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>M1_2.3_time</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>M1_2.4_score</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>M1_2.4_time</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>M1_2.5_EOU</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>M1_2.6_effort</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>M1_3.1_score</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>M1_3.1_time</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>M1_3.2_score</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>M1_3.2_time</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>M1_3.3_score</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>M1_3.3_time</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>M1_3.4_score</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>M1_3.4_time</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>M1_3.5_score</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>M1_3.5_time</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>M1_3.6_EOU</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>M1_3.7_effort</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>M1_4.1_score</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>M1_4.1_time</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>M1_4.2_score</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>M1_4.2_time</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>M1_4.3_score</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>M1_4.3_time</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>M1_4.4_score</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>M1_4.4_time</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>M1_4.5_EOU</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>M1_4.6_effort</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>M1_5.1_score</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>M1_5.1_time</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>M1_5.2_score</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>M1_5.2_time</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>M1_5.3_EOU</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>M1_5.4_effort</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>M1_6.1_score</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>M1_6.1_time</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>M1_6.2_score</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>M1_6.2_time</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>M1_6.3_EOU</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>M1_6.4_effort</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>M1_SSI_1</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>M1_SSI_3</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>M1_SSI_9</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>M1_SSI_10</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>M1_adverse_events</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>M1_total_score</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>M1_competence_score</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>M1_adaptability_score</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>M1_self_esteem_score</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>M2_1.1_score</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>M2_1.1_time</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>M2_1.2_score</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>M2_1.2_time</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>M2_1.3_score</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>M2_1.3_time</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>M2_1.4_EOU</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>M2_1.5_effort</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>M2_2.1_score</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>M2_2.1_time</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>M2_2.2_score</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>M2_2.2_time</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>M2_2.3_score</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>M2_2.3_time</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>M2_2.4_score</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>M2_2.4_time</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>M2_2.5_EOU</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>M2_2.6_effort</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>M2_3.1_score</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>M2_3.1_time</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>M2_3.2_score</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>M2_3.2_time</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>M2_3.3_score</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>M2_3.3_time</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>M2_3.4_score</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>M2_3.4_time</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>M2_3.5_score</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>M2_3.5_time</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>M2_3.6_EOU</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>M2_3.7_effort</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>M2_4.1_score</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>M2_4.1_time</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>M2_4.2_score</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>M2_4.2_time</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>M2_4.3_score</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>M2_4.3_time</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>M2_4.4_score</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>M2_4.4_time</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>M2_4.5_EOU</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>M2_4.6_effort</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>M2_5.1_score</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>M2_5.1_time</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>M2_5.2_score</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>M2_5.2_time</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>M2_5.3_EOU</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>M2_5.4_effort</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>M2_6.1_score</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>M2_6.1_time</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>M2_6.2_score</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>M2_6.2_time</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>M2_6.3_EOU</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>M2_6.4_effort</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>M2_SSI_1</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>M2_SSI_3</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>M2_SSI_9</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>M2_SSI_10</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>M2_adverse_events</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>M2_total_score</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>M2_competence_score</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>M2_adaptability_score</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>M2_self_esteem_score</t>
         </is>
@@ -1143,7 +1153,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15/10/1957</t>
+          <t>15.10.1957</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1181,54 +1191,58 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Manual wheelchair at home</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Electric wheelchair for 2 years, for outdoor</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>30</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
         <v>32</v>
       </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6</v>
+      </c>
       <c r="AB2" t="n">
         <v>3</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
@@ -1236,23 +1250,23 @@
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
         <v>5</v>
       </c>
-      <c r="AI2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3</v>
-      </c>
       <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="n">
         <v>105</v>
       </c>
-      <c r="AL2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
@@ -1264,69 +1278,67 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
         <v>4</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AW2" t="n">
         <v>4</v>
       </c>
-      <c r="AV2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6</v>
-      </c>
       <c r="AX2" t="n">
         <v>3</v>
       </c>
       <c r="AY2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA2" t="n">
         <v>11</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC2" t="n">
         <v>160</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BD2" t="n">
         <v>1</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BE2" t="n">
         <v>90</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BF2" t="n">
         <v>4</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BG2" t="n">
         <v>5</v>
       </c>
-      <c r="BF2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
         <v>3</v>
       </c>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BK2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM2" t="n">
         <v>4</v>
       </c>
-      <c r="BL2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
         <v>3</v>
       </c>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="n">
         <v>7</v>
       </c>
@@ -1334,121 +1346,121 @@
         <v>6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
         <v>6</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BW2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
         <v>1.423</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.25</v>
       </c>
       <c r="CA2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CB2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD2" t="n">
         <v>55</v>
       </c>
-      <c r="CC2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF2" t="n">
         <v>26</v>
       </c>
-      <c r="CE2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH2" t="n">
         <v>15</v>
       </c>
-      <c r="CG2" t="n">
-        <v>7</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>7</v>
-      </c>
       <c r="CI2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CJ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL2" t="n">
         <v>20</v>
       </c>
-      <c r="CK2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN2" t="n">
         <v>21</v>
       </c>
-      <c r="CM2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP2" t="n">
         <v>8</v>
       </c>
-      <c r="CO2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR2" t="n">
         <v>40</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CS2" t="n">
         <v>5</v>
       </c>
-      <c r="CR2" t="n">
-        <v>6</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>3</v>
-      </c>
       <c r="CT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV2" t="n">
         <v>58</v>
       </c>
-      <c r="CU2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX2" t="n">
         <v>32</v>
       </c>
-      <c r="CW2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX2" t="n">
+      <c r="CY2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ2" t="n">
         <v>86</v>
       </c>
-      <c r="CY2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB2" t="n">
         <v>147</v>
       </c>
-      <c r="DA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD2" t="n">
         <v>104</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DE2" t="n">
         <v>5</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DF2" t="n">
         <v>5</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>10</v>
       </c>
       <c r="DG2" t="n">
         <v>3</v>
@@ -1457,64 +1469,70 @@
         <v>10</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>10</v>
+      </c>
       <c r="DK2" t="n">
         <v>0</v>
       </c>
       <c r="DL2" t="inlineStr"/>
       <c r="DM2" t="n">
-        <v>7</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr"/>
       <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>7</v>
+      </c>
       <c r="DQ2" t="n">
         <v>0</v>
       </c>
       <c r="DR2" t="inlineStr"/>
-      <c r="DS2" t="inlineStr"/>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
       <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
+      <c r="DU2" t="inlineStr"/>
       <c r="DV2" t="inlineStr"/>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="inlineStr"/>
-      <c r="DY2" t="inlineStr"/>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="n">
-        <v>7</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>6</v>
-      </c>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
       <c r="EC2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="ED2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="EF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
         <v>1.577</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EI2" t="n">
         <v>1.167</v>
       </c>
-      <c r="EH2" t="n">
+      <c r="EJ2" t="n">
         <v>1.667</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="EK2" t="n">
         <v>2.125</v>
       </c>
     </row>
@@ -1536,7 +1554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06/05/1963</t>
+          <t>06.05.1963</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1574,360 +1592,368 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Manual wheelchair with Swiss-trac</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>29</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
         <v>37</v>
       </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" t="n">
         <v>27</v>
       </c>
-      <c r="V3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" t="n">
         <v>25</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
       <c r="AA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="n">
         <v>40</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" t="n">
         <v>27</v>
       </c>
-      <c r="AD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" t="n">
         <v>18</v>
       </c>
-      <c r="AF3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="n">
         <v>55</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>5</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3</v>
-      </c>
       <c r="AK3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" t="n">
         <v>63</v>
       </c>
-      <c r="AL3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="n">
         <v>60</v>
       </c>
-      <c r="AN3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>50</v>
       </c>
-      <c r="AP3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" t="n">
         <v>40</v>
       </c>
-      <c r="AR3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
         <v>91</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AV3" t="n">
         <v>5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3</v>
-      </c>
       <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AX3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA3" t="n">
         <v>13</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>7</v>
+      </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="n">
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="n">
         <v>4</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>6</v>
       </c>
       <c r="BU3" t="n">
         <v>5</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BW3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>2.167</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CA3" t="n">
         <v>2.5</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CB3" t="n">
         <v>1.375</v>
       </c>
-      <c r="CA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB3" t="n">
+      <c r="CC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD3" t="n">
         <v>30</v>
       </c>
-      <c r="CC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD3" t="n">
+      <c r="CE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF3" t="n">
         <v>20</v>
       </c>
-      <c r="CE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF3" t="n">
+      <c r="CG3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH3" t="n">
         <v>22</v>
       </c>
-      <c r="CG3" t="n">
-        <v>6</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>7</v>
-      </c>
       <c r="CI3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CJ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL3" t="n">
         <v>21</v>
       </c>
-      <c r="CK3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL3" t="n">
+      <c r="CM3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN3" t="n">
         <v>17</v>
       </c>
-      <c r="CM3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN3" t="n">
+      <c r="CO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP3" t="n">
         <v>10</v>
       </c>
-      <c r="CO3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CP3" t="n">
+      <c r="CQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR3" t="n">
         <v>22</v>
       </c>
-      <c r="CQ3" t="n">
+      <c r="CS3" t="n">
         <v>5</v>
       </c>
-      <c r="CR3" t="n">
-        <v>7</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>3</v>
-      </c>
       <c r="CT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV3" t="n">
         <v>68</v>
       </c>
-      <c r="CU3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV3" t="n">
+      <c r="CW3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX3" t="n">
         <v>83</v>
       </c>
-      <c r="CW3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX3" t="n">
+      <c r="CY3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ3" t="n">
         <v>100</v>
       </c>
-      <c r="CY3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ3" t="n">
+      <c r="DA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB3" t="n">
         <v>140</v>
       </c>
-      <c r="DA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB3" t="n">
+      <c r="DC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD3" t="n">
         <v>135</v>
       </c>
-      <c r="DC3" t="n">
+      <c r="DE3" t="n">
         <v>5</v>
       </c>
-      <c r="DD3" t="n">
+      <c r="DF3" t="n">
         <v>5</v>
       </c>
-      <c r="DE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>6</v>
-      </c>
       <c r="DG3" t="n">
         <v>3</v>
       </c>
       <c r="DH3" t="n">
+        <v>6</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ3" t="n">
         <v>9</v>
       </c>
-      <c r="DI3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DJ3" t="n">
+      <c r="DK3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL3" t="n">
         <v>95</v>
       </c>
-      <c r="DK3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DL3" t="n">
+      <c r="DM3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN3" t="n">
         <v>80</v>
       </c>
-      <c r="DM3" t="n">
+      <c r="DO3" t="n">
         <v>5</v>
       </c>
-      <c r="DN3" t="n">
+      <c r="DP3" t="n">
         <v>5</v>
       </c>
-      <c r="DO3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DP3" t="n">
+      <c r="DQ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR3" t="n">
         <v>77</v>
       </c>
-      <c r="DQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR3" t="n">
+      <c r="DS3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT3" t="n">
         <v>45</v>
       </c>
-      <c r="DS3" t="n">
-        <v>7</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>6</v>
-      </c>
       <c r="DU3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="DV3" t="n">
+        <v>6</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX3" t="n">
         <v>130</v>
       </c>
-      <c r="DW3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DX3" t="n">
+      <c r="DY3" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ3" t="n">
         <v>74</v>
       </c>
-      <c r="DY3" t="n">
-        <v>7</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>7</v>
-      </c>
       <c r="EA3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="EB3" t="n">
         <v>7</v>
       </c>
       <c r="EC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>7</v>
+      </c>
+      <c r="EE3" t="n">
         <v>5</v>
       </c>
-      <c r="ED3" t="n">
-        <v>7</v>
-      </c>
-      <c r="EE3" t="n">
-        <v>0</v>
-      </c>
       <c r="EF3" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH3" t="n">
         <v>2.846</v>
       </c>
-      <c r="EG3" t="n">
+      <c r="EI3" t="n">
         <v>2.75</v>
       </c>
-      <c r="EH3" t="n">
-        <v>3</v>
-      </c>
-      <c r="EI3" t="n">
+      <c r="EJ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="EK3" t="n">
         <v>2.875</v>
       </c>
     </row>
@@ -1949,7 +1975,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15/04/1969</t>
+          <t>15.04.1969</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1987,166 +2013,168 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Manual wheelchair at home</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Zeisel for outdoor, e-fix in the clinic</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>29</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
         <v>44</v>
       </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
         <v>35</v>
       </c>
-      <c r="V4" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
         <v>15</v>
       </c>
-      <c r="X4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7</v>
-      </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="n">
         <v>26</v>
       </c>
-      <c r="AB4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
         <v>17</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
         <v>8</v>
       </c>
-      <c r="AF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="n">
         <v>12</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>5</v>
       </c>
-      <c r="AI4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2</v>
-      </c>
       <c r="AK4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="n">
         <v>85</v>
       </c>
-      <c r="AL4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
         <v>26</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
         <v>1</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AQ4" t="n">
         <v>245</v>
       </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" t="n">
         <v>88</v>
       </c>
-      <c r="AR4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="n">
         <v>83</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AV4" t="n">
         <v>5</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3</v>
-      </c>
       <c r="AW4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY4" t="n">
         <v>10</v>
       </c>
-      <c r="AX4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA4" t="n">
         <v>8</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>7</v>
+      </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
       <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>7</v>
-      </c>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="n">
         <v>7</v>
       </c>
@@ -2154,176 +2182,176 @@
         <v>7</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BW4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
         <v>1.923</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="BZ4" t="n">
         <v>1.91</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CA4" t="n">
         <v>1.83</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>3</v>
-      </c>
       <c r="CB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD4" t="n">
         <v>50</v>
       </c>
-      <c r="CC4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD4" t="n">
+      <c r="CE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF4" t="n">
         <v>16</v>
       </c>
-      <c r="CE4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF4" t="n">
+      <c r="CG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH4" t="n">
         <v>44</v>
       </c>
-      <c r="CG4" t="n">
-        <v>7</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>7</v>
-      </c>
       <c r="CI4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CJ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL4" t="n">
         <v>20</v>
       </c>
-      <c r="CK4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL4" t="n">
+      <c r="CM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN4" t="n">
         <v>17</v>
       </c>
-      <c r="CM4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>6</v>
-      </c>
       <c r="CO4" t="n">
         <v>3</v>
       </c>
       <c r="CP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR4" t="n">
         <v>18</v>
       </c>
-      <c r="CQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>7</v>
-      </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV4" t="n">
         <v>63</v>
       </c>
-      <c r="CU4" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV4" t="n">
+      <c r="CW4" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX4" t="n">
         <v>45</v>
       </c>
-      <c r="CW4" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX4" t="n">
+      <c r="CY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ4" t="n">
         <v>244</v>
       </c>
-      <c r="CY4" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ4" t="n">
+      <c r="DA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB4" t="n">
         <v>196</v>
       </c>
-      <c r="DA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB4" t="n">
+      <c r="DC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD4" t="n">
         <v>60</v>
       </c>
-      <c r="DC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>7</v>
-      </c>
       <c r="DE4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="DF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH4" t="n">
         <v>8</v>
       </c>
-      <c r="DG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH4" t="n">
+      <c r="DI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ4" t="n">
         <v>9</v>
       </c>
-      <c r="DI4" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ4" t="n">
+      <c r="DK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL4" t="n">
         <v>210</v>
       </c>
-      <c r="DK4" t="n">
-        <v>3</v>
-      </c>
-      <c r="DL4" t="n">
+      <c r="DM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN4" t="n">
         <v>117</v>
       </c>
-      <c r="DM4" t="n">
+      <c r="DO4" t="n">
         <v>5</v>
       </c>
-      <c r="DN4" t="n">
-        <v>6</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>2</v>
-      </c>
       <c r="DP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DR4" t="n">
         <v>214</v>
       </c>
-      <c r="DQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR4" t="n">
+      <c r="DS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT4" t="n">
         <v>47</v>
       </c>
-      <c r="DS4" t="n">
+      <c r="DU4" t="n">
         <v>5</v>
       </c>
-      <c r="DT4" t="n">
-        <v>6</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>3</v>
-      </c>
       <c r="DV4" t="n">
+        <v>6</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX4" t="n">
         <v>104</v>
       </c>
-      <c r="DW4" t="n">
-        <v>3</v>
-      </c>
-      <c r="DX4" t="n">
+      <c r="DY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ4" t="n">
         <v>72</v>
       </c>
-      <c r="DY4" t="n">
-        <v>7</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>7</v>
-      </c>
       <c r="EA4" t="n">
         <v>7</v>
       </c>
@@ -2337,18 +2365,24 @@
         <v>7</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="EF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH4" t="n">
         <v>1.962</v>
       </c>
-      <c r="EG4" t="n">
+      <c r="EI4" t="n">
         <v>1.917</v>
       </c>
-      <c r="EH4" t="n">
-        <v>2</v>
-      </c>
-      <c r="EI4" t="n">
+      <c r="EJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="EK4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2408,364 +2442,372 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>manual wheelchair since a few months</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>27</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
         <v>35</v>
       </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
         <v>17</v>
       </c>
-      <c r="V5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
         <v>28</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
       <c r="AA5" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
         <v>20</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>7</v>
-      </c>
       <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>20</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>4</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>5</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
         <v>110</v>
       </c>
-      <c r="AL5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="n">
         <v>43</v>
       </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>100</v>
       </c>
-      <c r="AP5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="n">
         <v>94</v>
       </c>
-      <c r="AR5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
         <v>108</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AV5" t="n">
         <v>4</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AW5" t="n">
         <v>4</v>
       </c>
-      <c r="AV5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" t="n">
         <v>12</v>
       </c>
-      <c r="AX5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA5" t="n">
         <v>9</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
         <v>5</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BG5" t="n">
         <v>5</v>
       </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
       <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BS5" t="n">
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU5" t="n">
         <v>4</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="BV5" t="n">
         <v>4</v>
       </c>
-      <c r="BU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
       <c r="BW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
         <v>1.231</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="BZ5" t="n">
         <v>1.25</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CA5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CB5" t="n">
         <v>1</v>
       </c>
-      <c r="CA5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB5" t="n">
+      <c r="CC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD5" t="n">
         <v>78</v>
       </c>
-      <c r="CC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD5" t="n">
+      <c r="CE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF5" t="n">
         <v>90</v>
       </c>
-      <c r="CE5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF5" t="n">
+      <c r="CG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH5" t="n">
         <v>25</v>
       </c>
-      <c r="CG5" t="n">
+      <c r="CI5" t="n">
         <v>4</v>
       </c>
-      <c r="CH5" t="n">
+      <c r="CJ5" t="n">
         <v>4</v>
       </c>
-      <c r="CI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CJ5" t="n">
+      <c r="CK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL5" t="n">
         <v>37</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CM5" t="n">
         <v>1</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CN5" t="n">
         <v>30</v>
       </c>
-      <c r="CM5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN5" t="n">
+      <c r="CO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP5" t="n">
         <v>9</v>
       </c>
-      <c r="CO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CP5" t="n">
+      <c r="CQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR5" t="n">
         <v>16</v>
       </c>
-      <c r="CQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CR5" t="n">
+      <c r="CS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT5" t="n">
         <v>4</v>
       </c>
-      <c r="CS5" t="n">
+      <c r="CU5" t="n">
         <v>1</v>
       </c>
-      <c r="CT5" t="n">
+      <c r="CV5" t="n">
         <v>65</v>
       </c>
-      <c r="CU5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV5" t="n">
+      <c r="CW5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX5" t="n">
         <v>20</v>
       </c>
-      <c r="CW5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX5" t="n">
+      <c r="CY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ5" t="n">
         <v>51</v>
       </c>
-      <c r="CY5" t="n">
+      <c r="DA5" t="n">
         <v>1</v>
       </c>
-      <c r="CZ5" t="n">
+      <c r="DB5" t="n">
         <v>187</v>
       </c>
-      <c r="DA5" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB5" t="n">
+      <c r="DC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD5" t="n">
         <v>96</v>
       </c>
-      <c r="DC5" t="n">
+      <c r="DE5" t="n">
         <v>5</v>
       </c>
-      <c r="DD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>3</v>
-      </c>
       <c r="DF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH5" t="n">
         <v>19</v>
       </c>
-      <c r="DG5" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH5" t="n">
+      <c r="DI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ5" t="n">
         <v>17</v>
       </c>
-      <c r="DI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ5" t="n">
+      <c r="DK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL5" t="n">
         <v>150</v>
       </c>
-      <c r="DK5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DL5" t="n">
+      <c r="DM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN5" t="n">
         <v>92</v>
       </c>
-      <c r="DM5" t="n">
+      <c r="DO5" t="n">
         <v>5</v>
       </c>
-      <c r="DN5" t="n">
+      <c r="DP5" t="n">
         <v>4</v>
       </c>
-      <c r="DO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP5" t="n">
+      <c r="DQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DR5" t="n">
         <v>120</v>
       </c>
-      <c r="DQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR5" t="n">
+      <c r="DS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT5" t="n">
         <v>48</v>
       </c>
-      <c r="DS5" t="n">
+      <c r="DU5" t="n">
         <v>4</v>
       </c>
-      <c r="DT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>2</v>
-      </c>
       <c r="DV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DX5" t="n">
         <v>128</v>
       </c>
-      <c r="DW5" t="n">
-        <v>3</v>
-      </c>
-      <c r="DX5" t="n">
+      <c r="DY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ5" t="n">
         <v>48</v>
       </c>
-      <c r="DY5" t="n">
+      <c r="EA5" t="n">
         <v>4</v>
       </c>
-      <c r="DZ5" t="n">
+      <c r="EB5" t="n">
         <v>4</v>
       </c>
-      <c r="EA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>6</v>
-      </c>
       <c r="EC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE5" t="n">
         <v>4</v>
       </c>
-      <c r="ED5" t="n">
-        <v>6</v>
-      </c>
-      <c r="EE5" t="n">
-        <v>0</v>
-      </c>
       <c r="EF5" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
         <v>0.731</v>
       </c>
-      <c r="EG5" t="n">
+      <c r="EI5" t="n">
         <v>0.5</v>
       </c>
-      <c r="EH5" t="n">
+      <c r="EJ5" t="n">
         <v>0.833</v>
       </c>
-      <c r="EI5" t="n">
+      <c r="EK5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2823,358 +2865,366 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>27</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
         <v>10</v>
       </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="n">
         <v>50</v>
       </c>
-      <c r="V6" t="n">
-        <v>3</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
         <v>85</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
       <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
         <v>36</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
         <v>31</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
         <v>10</v>
       </c>
-      <c r="AF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="n">
         <v>30</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>4</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>5</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" t="n">
         <v>103</v>
       </c>
-      <c r="AL6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
         <v>42</v>
       </c>
-      <c r="AN6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>38</v>
       </c>
-      <c r="AP6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
         <v>260</v>
       </c>
-      <c r="AR6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
         <v>92</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3</v>
-      </c>
       <c r="AV6" t="n">
         <v>3</v>
       </c>
       <c r="AW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" t="n">
         <v>16</v>
       </c>
-      <c r="AX6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA6" t="n">
         <v>11</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC6" t="n">
         <v>243</v>
       </c>
-      <c r="BB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE6" t="n">
         <v>71</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BF6" t="n">
         <v>4</v>
       </c>
-      <c r="BE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2</v>
-      </c>
       <c r="BG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI6" t="n">
         <v>322</v>
       </c>
-      <c r="BH6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI6" t="n">
+      <c r="BJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK6" t="n">
         <v>47</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>2</v>
-      </c>
       <c r="BL6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO6" t="n">
         <v>351</v>
       </c>
-      <c r="BN6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO6" t="n">
+      <c r="BP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>73</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BR6" t="n">
         <v>5</v>
       </c>
-      <c r="BQ6" t="n">
+      <c r="BS6" t="n">
         <v>4</v>
       </c>
-      <c r="BR6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BS6" t="n">
+      <c r="BT6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU6" t="n">
         <v>5</v>
       </c>
-      <c r="BT6" t="n">
+      <c r="BV6" t="n">
         <v>4</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="BW6" t="n">
         <v>4</v>
       </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW6" t="n">
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
         <v>0.077</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="BZ6" t="n">
         <v>-0.167</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CA6" t="n">
         <v>0.333</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CB6" t="n">
         <v>0.25</v>
       </c>
-      <c r="CA6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB6" t="n">
+      <c r="CC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD6" t="n">
         <v>10</v>
       </c>
-      <c r="CC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD6" t="n">
+      <c r="CE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF6" t="n">
         <v>130</v>
       </c>
-      <c r="CE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF6" t="n">
+      <c r="CG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH6" t="n">
         <v>15</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CI6" t="n">
         <v>5</v>
       </c>
-      <c r="CH6" t="n">
-        <v>6</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>2</v>
-      </c>
       <c r="CJ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL6" t="n">
         <v>29</v>
       </c>
-      <c r="CK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL6" t="n">
+      <c r="CM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN6" t="n">
         <v>27</v>
       </c>
-      <c r="CM6" t="n">
+      <c r="CO6" t="n">
         <v>1</v>
       </c>
-      <c r="CN6" t="n">
+      <c r="CP6" t="n">
         <v>30</v>
       </c>
-      <c r="CO6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CP6" t="n">
+      <c r="CQ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR6" t="n">
         <v>75</v>
       </c>
-      <c r="CQ6" t="n">
+      <c r="CS6" t="n">
         <v>4</v>
       </c>
-      <c r="CR6" t="n">
+      <c r="CT6" t="n">
         <v>5</v>
       </c>
-      <c r="CS6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT6" t="n">
+      <c r="CU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV6" t="n">
         <v>55</v>
       </c>
-      <c r="CU6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV6" t="n">
+      <c r="CW6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX6" t="n">
         <v>16</v>
       </c>
-      <c r="CW6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX6" t="n">
+      <c r="CY6" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ6" t="n">
         <v>50</v>
       </c>
-      <c r="CY6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ6" t="n">
+      <c r="DA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB6" t="n">
         <v>183</v>
       </c>
-      <c r="DA6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB6" t="n">
+      <c r="DC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD6" t="n">
         <v>103</v>
       </c>
-      <c r="DC6" t="n">
+      <c r="DE6" t="n">
         <v>5</v>
       </c>
-      <c r="DD6" t="n">
+      <c r="DF6" t="n">
         <v>4</v>
       </c>
-      <c r="DE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF6" t="n">
+      <c r="DG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH6" t="n">
         <v>16</v>
       </c>
-      <c r="DG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH6" t="n">
+      <c r="DI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ6" t="n">
         <v>14</v>
       </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="inlineStr"/>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="inlineStr"/>
       <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="n">
         <v>5</v>
       </c>
-      <c r="DN6" t="n">
+      <c r="DP6" t="n">
         <v>5</v>
       </c>
-      <c r="DO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP6" t="inlineStr"/>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="inlineStr"/>
-      <c r="DS6" t="inlineStr"/>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
       <c r="DT6" t="inlineStr"/>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
+      <c r="DU6" t="inlineStr"/>
       <c r="DV6" t="inlineStr"/>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="inlineStr"/>
-      <c r="DY6" t="inlineStr"/>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ6" t="inlineStr"/>
-      <c r="EA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>5</v>
-      </c>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
       <c r="EC6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="ED6" t="n">
         <v>5</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="EF6" t="n">
+        <v>5</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
         <v>-0.115</v>
       </c>
-      <c r="EG6" t="n">
+      <c r="EI6" t="n">
         <v>-0.333</v>
       </c>
-      <c r="EH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI6" t="n">
+      <c r="EJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK6" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -3234,172 +3284,174 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>manual wheelchair at home since 2 years</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>28</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
         <v>17</v>
       </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="n">
         <v>10</v>
       </c>
-      <c r="V7" t="n">
-        <v>3</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
         <v>21</v>
       </c>
-      <c r="X7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>7</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="n">
         <v>26</v>
       </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" t="n">
         <v>15</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" t="n">
         <v>4</v>
       </c>
-      <c r="AF7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
         <v>23</v>
       </c>
-      <c r="AH7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AK7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" t="n">
         <v>74</v>
       </c>
-      <c r="AL7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO7" t="n">
         <v>20</v>
       </c>
-      <c r="AN7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>184</v>
       </c>
-      <c r="AP7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" t="n">
         <v>42</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
         <v>129</v>
       </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
       <c r="AV7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" t="n">
         <v>12</v>
       </c>
-      <c r="AX7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA7" t="n">
         <v>10</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" t="n">
         <v>113</v>
       </c>
-      <c r="BB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE7" t="n">
         <v>90</v>
       </c>
-      <c r="BD7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7</v>
-      </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BG7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI7" t="n">
         <v>140</v>
       </c>
-      <c r="BH7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI7" t="n">
+      <c r="BJ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK7" t="n">
         <v>57</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7</v>
-      </c>
       <c r="BL7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BM7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO7" t="n">
         <v>155</v>
       </c>
-      <c r="BN7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO7" t="n">
+      <c r="BP7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>102</v>
       </c>
-      <c r="BP7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7</v>
-      </c>
       <c r="BR7" t="n">
         <v>7</v>
       </c>
@@ -3413,115 +3465,115 @@
         <v>7</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
         <v>2.423</v>
       </c>
-      <c r="BX7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>3</v>
-      </c>
       <c r="BZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB7" t="n">
         <v>2.625</v>
       </c>
-      <c r="CA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB7" t="n">
+      <c r="CC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD7" t="n">
         <v>43</v>
       </c>
-      <c r="CC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD7" t="n">
+      <c r="CE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF7" t="n">
         <v>30</v>
       </c>
-      <c r="CE7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF7" t="n">
+      <c r="CG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH7" t="n">
         <v>11</v>
       </c>
-      <c r="CG7" t="n">
-        <v>7</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>7</v>
-      </c>
       <c r="CI7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CJ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL7" t="n">
         <v>17</v>
       </c>
-      <c r="CK7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL7" t="n">
+      <c r="CM7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN7" t="n">
         <v>19</v>
       </c>
-      <c r="CM7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN7" t="n">
+      <c r="CO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP7" t="n">
         <v>8</v>
       </c>
-      <c r="CO7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CP7" t="n">
+      <c r="CQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR7" t="n">
         <v>22</v>
       </c>
-      <c r="CQ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>7</v>
-      </c>
       <c r="CS7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV7" t="n">
         <v>41</v>
       </c>
-      <c r="CU7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV7" t="n">
+      <c r="CW7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX7" t="n">
         <v>12</v>
       </c>
-      <c r="CW7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX7" t="n">
+      <c r="CY7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ7" t="n">
         <v>89</v>
       </c>
-      <c r="CY7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ7" t="n">
+      <c r="DA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB7" t="n">
         <v>67</v>
       </c>
-      <c r="DA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB7" t="n">
+      <c r="DC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD7" t="n">
         <v>66</v>
       </c>
-      <c r="DC7" t="n">
-        <v>7</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>7</v>
-      </c>
       <c r="DE7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="DF7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="DG7" t="n">
         <v>3</v>
@@ -3530,64 +3582,70 @@
         <v>10</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>10</v>
+      </c>
       <c r="DK7" t="n">
         <v>0</v>
       </c>
       <c r="DL7" t="inlineStr"/>
       <c r="DM7" t="n">
-        <v>7</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DN7" t="inlineStr"/>
       <c r="DO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP7" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>7</v>
+      </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="inlineStr"/>
-      <c r="DS7" t="inlineStr"/>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
       <c r="DT7" t="inlineStr"/>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
+      <c r="DU7" t="inlineStr"/>
       <c r="DV7" t="inlineStr"/>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="inlineStr"/>
-      <c r="DY7" t="inlineStr"/>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ7" t="inlineStr"/>
-      <c r="EA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>6</v>
-      </c>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
       <c r="EC7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="ED7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="EF7" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH7" t="n">
         <v>2.846</v>
       </c>
-      <c r="EG7" t="n">
+      <c r="EI7" t="n">
         <v>2.833</v>
       </c>
-      <c r="EH7" t="n">
-        <v>3</v>
-      </c>
-      <c r="EI7" t="n">
+      <c r="EJ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="EK7" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -3647,180 +3705,182 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>magic Mobility since 2 years extreme x8</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>28</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
         <v>23</v>
       </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="n">
         <v>164</v>
       </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
         <v>53</v>
       </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3</v>
-      </c>
       <c r="Z8" t="n">
         <v>3</v>
       </c>
       <c r="AA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC8" t="n">
         <v>41</v>
       </c>
-      <c r="AB8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
         <v>18</v>
       </c>
-      <c r="AD8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="n">
         <v>13</v>
       </c>
-      <c r="AF8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI8" t="n">
         <v>20</v>
       </c>
-      <c r="AH8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>6</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM8" t="n">
         <v>242</v>
       </c>
-      <c r="AL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
         <v>228</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AP8" t="n">
         <v>1</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AQ8" t="n">
         <v>700</v>
       </c>
-      <c r="AP8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="n">
         <v>255</v>
       </c>
-      <c r="AR8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
         <v>154</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AV8" t="n">
         <v>5</v>
       </c>
-      <c r="AU8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3</v>
-      </c>
       <c r="AW8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY8" t="n">
         <v>15</v>
       </c>
-      <c r="AX8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA8" t="n">
         <v>12</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC8" t="n">
         <v>175</v>
       </c>
-      <c r="BB8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE8" t="n">
         <v>148</v>
       </c>
-      <c r="BD8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE8" t="n">
+      <c r="BF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>5</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG8" t="n">
+      <c r="BH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI8" t="n">
         <v>180</v>
       </c>
-      <c r="BH8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI8" t="n">
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
         <v>64</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>4</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BM8" t="n">
         <v>5</v>
       </c>
-      <c r="BL8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO8" t="n">
         <v>138</v>
       </c>
-      <c r="BN8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO8" t="n">
+      <c r="BP8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>111</v>
       </c>
-      <c r="BP8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6</v>
-      </c>
       <c r="BR8" t="n">
         <v>6</v>
       </c>
@@ -3828,187 +3888,193 @@
         <v>6</v>
       </c>
       <c r="BT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV8" t="n">
         <v>5</v>
       </c>
-      <c r="BU8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
       <c r="BW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
         <v>2.192</v>
       </c>
-      <c r="BX8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY8" t="n">
+      <c r="BZ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA8" t="n">
         <v>1.833</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CB8" t="n">
         <v>2.75</v>
       </c>
-      <c r="CA8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB8" t="n">
+      <c r="CC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD8" t="n">
         <v>14</v>
       </c>
-      <c r="CC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD8" t="n">
+      <c r="CE8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF8" t="n">
         <v>32</v>
       </c>
-      <c r="CE8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF8" t="n">
+      <c r="CG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH8" t="n">
         <v>13</v>
       </c>
-      <c r="CG8" t="n">
-        <v>7</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>7</v>
-      </c>
       <c r="CI8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CJ8" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL8" t="n">
         <v>16</v>
       </c>
-      <c r="CK8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL8" t="n">
+      <c r="CM8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN8" t="n">
         <v>12</v>
       </c>
-      <c r="CM8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>7</v>
-      </c>
       <c r="CO8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP8" t="n">
+        <v>7</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR8" t="n">
         <v>31</v>
       </c>
-      <c r="CQ8" t="n">
+      <c r="CS8" t="n">
         <v>5</v>
       </c>
-      <c r="CR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>3</v>
-      </c>
       <c r="CT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV8" t="n">
         <v>48</v>
       </c>
-      <c r="CU8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV8" t="n">
+      <c r="CW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX8" t="n">
         <v>23</v>
       </c>
-      <c r="CW8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX8" t="n">
+      <c r="CY8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ8" t="n">
         <v>102</v>
       </c>
-      <c r="CY8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ8" t="n">
+      <c r="DA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB8" t="n">
         <v>33</v>
       </c>
-      <c r="DA8" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB8" t="n">
+      <c r="DC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD8" t="n">
         <v>95</v>
       </c>
-      <c r="DC8" t="n">
-        <v>6</v>
-      </c>
-      <c r="DD8" t="n">
+      <c r="DE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="DF8" t="n">
         <v>5</v>
       </c>
-      <c r="DE8" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF8" t="n">
+      <c r="DG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH8" t="n">
         <v>14</v>
       </c>
-      <c r="DG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH8" t="n">
+      <c r="DI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ8" t="n">
         <v>12</v>
       </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="inlineStr"/>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="inlineStr"/>
       <c r="DM8" t="n">
-        <v>7</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DN8" t="inlineStr"/>
       <c r="DO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>7</v>
+      </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="inlineStr"/>
-      <c r="DS8" t="inlineStr"/>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
       <c r="DT8" t="inlineStr"/>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
+      <c r="DU8" t="inlineStr"/>
       <c r="DV8" t="inlineStr"/>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="inlineStr"/>
-      <c r="DY8" t="inlineStr"/>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ8" t="inlineStr"/>
-      <c r="EA8" t="n">
-        <v>7</v>
-      </c>
-      <c r="EB8" t="n">
-        <v>7</v>
-      </c>
+      <c r="EA8" t="inlineStr"/>
+      <c r="EB8" t="inlineStr"/>
       <c r="EC8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="ED8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="EF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
         <v>1.808</v>
       </c>
-      <c r="EG8" t="n">
+      <c r="EI8" t="n">
         <v>1.75</v>
       </c>
-      <c r="EH8" t="n">
+      <c r="EJ8" t="n">
         <v>1.833</v>
       </c>
-      <c r="EI8" t="n">
+      <c r="EK8" t="n">
         <v>1.875</v>
       </c>
     </row>
@@ -4068,364 +4134,372 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>few days</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>28</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
         <v>9</v>
       </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="n">
         <v>22</v>
       </c>
-      <c r="V9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
         <v>30</v>
       </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA9" t="n">
         <v>5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
         <v>46</v>
       </c>
-      <c r="AB9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE9" t="n">
         <v>24</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="n">
         <v>14</v>
       </c>
-      <c r="AF9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
         <v>27</v>
       </c>
-      <c r="AH9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" t="n">
         <v>193</v>
       </c>
-      <c r="AL9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="n">
         <v>84</v>
       </c>
-      <c r="AN9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>300</v>
       </c>
-      <c r="AP9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="n">
         <v>187</v>
       </c>
-      <c r="AR9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" t="n">
         <v>134</v>
       </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>5</v>
       </c>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY9" t="n">
         <v>19</v>
       </c>
-      <c r="AX9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="n">
         <v>14</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
         <v>140</v>
       </c>
-      <c r="BB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC9" t="n">
+      <c r="BD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE9" t="n">
         <v>65</v>
       </c>
-      <c r="BD9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE9" t="n">
+      <c r="BF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4</v>
       </c>
-      <c r="BF9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG9" t="n">
+      <c r="BH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI9" t="n">
         <v>145</v>
       </c>
-      <c r="BH9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI9" t="n">
+      <c r="BJ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK9" t="n">
         <v>50</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BK9" t="n">
+      <c r="BL9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM9" t="n">
         <v>4</v>
       </c>
-      <c r="BL9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO9" t="n">
         <v>133</v>
       </c>
-      <c r="BN9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO9" t="n">
+      <c r="BP9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>73</v>
       </c>
-      <c r="BP9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ9" t="n">
+      <c r="BR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS9" t="n">
         <v>5</v>
       </c>
-      <c r="BR9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7</v>
-      </c>
       <c r="BT9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
         <v>7</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BW9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
         <v>2.077</v>
       </c>
-      <c r="BX9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA9" t="n">
         <v>2.333</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>3</v>
-      </c>
       <c r="CB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD9" t="n">
         <v>10</v>
       </c>
-      <c r="CC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD9" t="n">
+      <c r="CE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF9" t="n">
         <v>45</v>
       </c>
-      <c r="CE9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF9" t="n">
+      <c r="CG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH9" t="n">
         <v>27</v>
       </c>
-      <c r="CG9" t="n">
-        <v>6</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>6</v>
-      </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CJ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL9" t="n">
         <v>46</v>
       </c>
-      <c r="CK9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL9" t="n">
+      <c r="CM9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN9" t="n">
         <v>30</v>
       </c>
-      <c r="CM9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>7</v>
-      </c>
       <c r="CO9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CP9" t="n">
+        <v>7</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR9" t="n">
         <v>54</v>
       </c>
-      <c r="CQ9" t="n">
+      <c r="CS9" t="n">
         <v>4</v>
       </c>
-      <c r="CR9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>2</v>
-      </c>
       <c r="CT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV9" t="n">
         <v>174</v>
       </c>
-      <c r="CU9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV9" t="n">
+      <c r="CW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX9" t="n">
         <v>21</v>
       </c>
-      <c r="CW9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX9" t="n">
+      <c r="CY9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ9" t="n">
         <v>128</v>
       </c>
-      <c r="CY9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ9" t="n">
+      <c r="DA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB9" t="n">
         <v>25</v>
       </c>
-      <c r="DA9" t="n">
+      <c r="DC9" t="n">
         <v>1</v>
       </c>
-      <c r="DB9" t="n">
+      <c r="DD9" t="n">
         <v>140</v>
       </c>
-      <c r="DC9" t="n">
+      <c r="DE9" t="n">
         <v>5</v>
       </c>
-      <c r="DD9" t="n">
+      <c r="DF9" t="n">
         <v>1</v>
       </c>
-      <c r="DE9" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF9" t="n">
+      <c r="DG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH9" t="n">
         <v>12</v>
       </c>
-      <c r="DG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH9" t="n">
+      <c r="DI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>9</v>
       </c>
-      <c r="DI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" t="inlineStr"/>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="inlineStr"/>
       <c r="DM9" t="n">
-        <v>6</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DN9" t="inlineStr"/>
       <c r="DO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP9" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>6</v>
+      </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="inlineStr"/>
-      <c r="DS9" t="inlineStr"/>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
       <c r="DT9" t="inlineStr"/>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
+      <c r="DU9" t="inlineStr"/>
       <c r="DV9" t="inlineStr"/>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="inlineStr"/>
-      <c r="DY9" t="inlineStr"/>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ9" t="inlineStr"/>
-      <c r="EA9" t="n">
-        <v>6</v>
-      </c>
-      <c r="EB9" t="n">
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED9" t="n">
         <v>5</v>
       </c>
-      <c r="EC9" t="n">
+      <c r="EE9" t="n">
         <v>4</v>
       </c>
-      <c r="ED9" t="n">
-        <v>6</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0</v>
-      </c>
       <c r="EF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH9" t="n">
         <v>2.077</v>
       </c>
-      <c r="EG9" t="n">
+      <c r="EI9" t="n">
         <v>2.417</v>
       </c>
-      <c r="EH9" t="n">
+      <c r="EJ9" t="n">
         <v>2.167</v>
       </c>
-      <c r="EI9" t="n">
+      <c r="EK9" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -4485,162 +4559,164 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>29</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
         <v>13</v>
       </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" t="n">
         <v>42</v>
       </c>
-      <c r="V10" t="n">
-        <v>3</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
         <v>28</v>
       </c>
-      <c r="X10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>6</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
         <v>33</v>
       </c>
-      <c r="AB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
         <v>40</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="n">
         <v>28</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="n">
         <v>146</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>5</v>
       </c>
-      <c r="AI10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>3</v>
-      </c>
       <c r="AK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" t="n">
         <v>48</v>
       </c>
-      <c r="AL10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO10" t="n">
         <v>37</v>
       </c>
-      <c r="AN10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>66</v>
       </c>
-      <c r="AP10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS10" t="n">
         <v>331</v>
       </c>
-      <c r="AR10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU10" t="n">
         <v>142</v>
       </c>
-      <c r="AT10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
       <c r="AV10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY10" t="n">
         <v>20</v>
       </c>
-      <c r="AX10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA10" t="n">
         <v>13</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
         <v>0</v>
       </c>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6</v>
+      </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
       <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
+      <c r="BL10" t="inlineStr"/>
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="n">
         <v>0</v>
       </c>
       <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7</v>
-      </c>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
       <c r="BT10" t="n">
         <v>7</v>
       </c>
@@ -4648,85 +4724,85 @@
         <v>7</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
         <v>2.5</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="BZ10" t="n">
         <v>2.5</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CA10" t="n">
         <v>2.667</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CB10" t="n">
         <v>2.375</v>
       </c>
-      <c r="CA10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB10" t="n">
+      <c r="CC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD10" t="n">
         <v>24</v>
       </c>
-      <c r="CC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD10" t="n">
+      <c r="CE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF10" t="n">
         <v>57</v>
       </c>
-      <c r="CE10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF10" t="n">
+      <c r="CG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH10" t="n">
         <v>86</v>
       </c>
-      <c r="CG10" t="n">
-        <v>6</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>7</v>
-      </c>
       <c r="CI10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CJ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL10" t="n">
         <v>39</v>
       </c>
-      <c r="CK10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL10" t="n">
+      <c r="CM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN10" t="n">
         <v>31</v>
       </c>
-      <c r="CM10" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN10" t="n">
+      <c r="CO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP10" t="n">
         <v>5</v>
       </c>
-      <c r="CO10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CP10" t="n">
+      <c r="CQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR10" t="n">
         <v>31</v>
       </c>
-      <c r="CQ10" t="n">
-        <v>6</v>
-      </c>
-      <c r="CR10" t="n">
+      <c r="CS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT10" t="n">
         <v>5</v>
       </c>
-      <c r="CS10" t="n">
-        <v>2</v>
-      </c>
-      <c r="CT10" t="n">
+      <c r="CU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV10" t="n">
         <v>212</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>42</v>
       </c>
       <c r="CW10" t="n">
         <v>3</v>
@@ -4735,28 +4811,28 @@
         <v>42</v>
       </c>
       <c r="CY10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CZ10" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB10" t="n">
         <v>270</v>
       </c>
-      <c r="DA10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB10" t="n">
+      <c r="DC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD10" t="n">
         <v>123</v>
       </c>
-      <c r="DC10" t="n">
-        <v>6</v>
-      </c>
-      <c r="DD10" t="n">
+      <c r="DE10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DF10" t="n">
         <v>5</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>16</v>
       </c>
       <c r="DG10" t="n">
         <v>3</v>
@@ -4765,84 +4841,90 @@
         <v>16</v>
       </c>
       <c r="DI10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DJ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL10" t="n">
         <v>150</v>
       </c>
-      <c r="DK10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DL10" t="n">
+      <c r="DM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN10" t="n">
         <v>110</v>
       </c>
-      <c r="DM10" t="n">
-        <v>6</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>6</v>
-      </c>
       <c r="DO10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="DP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR10" t="n">
         <v>62</v>
       </c>
-      <c r="DQ10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DR10" t="n">
+      <c r="DS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT10" t="n">
         <v>48</v>
       </c>
-      <c r="DS10" t="n">
-        <v>6</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>6</v>
-      </c>
       <c r="DU10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="DV10" t="n">
+        <v>6</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DX10" t="n">
         <v>155</v>
       </c>
-      <c r="DW10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DX10" t="n">
+      <c r="DY10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ10" t="n">
         <v>82</v>
       </c>
-      <c r="DY10" t="n">
-        <v>6</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>7</v>
-      </c>
       <c r="EA10" t="n">
         <v>6</v>
       </c>
       <c r="EB10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="EC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE10" t="n">
         <v>5</v>
       </c>
-      <c r="ED10" t="n">
-        <v>6</v>
-      </c>
-      <c r="EE10" t="n">
-        <v>0</v>
-      </c>
       <c r="EF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
         <v>2.308</v>
       </c>
-      <c r="EG10" t="n">
+      <c r="EI10" t="n">
         <v>2.333</v>
       </c>
-      <c r="EH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="EI10" t="n">
+      <c r="EJ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="EK10" t="n">
         <v>1.75</v>
       </c>
     </row>
@@ -4852,144 +4934,422 @@
           <t>P10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>28.08.1954</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Stroke</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>68kg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2 (left), 0 (right)</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>one year</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>29</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>32</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>168</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>143</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>332</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
       <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
       <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
       <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
       <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
       <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
       <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="inlineStr"/>
-      <c r="BV11" t="inlineStr"/>
-      <c r="BW11" t="inlineStr"/>
-      <c r="BX11" t="inlineStr"/>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
-      <c r="CA11" t="inlineStr"/>
-      <c r="CB11" t="inlineStr"/>
-      <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="inlineStr"/>
-      <c r="CE11" t="inlineStr"/>
+      <c r="BT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>2</v>
+      </c>
       <c r="CF11" t="inlineStr"/>
-      <c r="CG11" t="inlineStr"/>
+      <c r="CG11" t="n">
+        <v>3</v>
+      </c>
       <c r="CH11" t="inlineStr"/>
-      <c r="CI11" t="inlineStr"/>
-      <c r="CJ11" t="inlineStr"/>
-      <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
+      <c r="CI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>26</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>16</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>68</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>3</v>
+      </c>
       <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="inlineStr"/>
-      <c r="DB11" t="inlineStr"/>
-      <c r="DC11" t="inlineStr"/>
-      <c r="DD11" t="inlineStr"/>
-      <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="inlineStr"/>
-      <c r="DI11" t="inlineStr"/>
-      <c r="DJ11" t="inlineStr"/>
-      <c r="DK11" t="inlineStr"/>
-      <c r="DL11" t="inlineStr"/>
-      <c r="DM11" t="inlineStr"/>
-      <c r="DN11" t="inlineStr"/>
-      <c r="DO11" t="inlineStr"/>
-      <c r="DP11" t="inlineStr"/>
-      <c r="DQ11" t="inlineStr"/>
-      <c r="DR11" t="inlineStr"/>
-      <c r="DS11" t="inlineStr"/>
-      <c r="DT11" t="inlineStr"/>
-      <c r="DU11" t="inlineStr"/>
-      <c r="DV11" t="inlineStr"/>
-      <c r="DW11" t="inlineStr"/>
-      <c r="DX11" t="inlineStr"/>
-      <c r="DY11" t="inlineStr"/>
-      <c r="DZ11" t="inlineStr"/>
-      <c r="EA11" t="inlineStr"/>
-      <c r="EB11" t="inlineStr"/>
-      <c r="EC11" t="inlineStr"/>
-      <c r="ED11" t="inlineStr"/>
-      <c r="EE11" t="inlineStr"/>
-      <c r="EF11" t="inlineStr"/>
-      <c r="EG11" t="inlineStr"/>
-      <c r="EH11" t="inlineStr"/>
-      <c r="EI11" t="inlineStr"/>
+      <c r="CW11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>137</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>150</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>128</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>7</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>112</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>7</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>95</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>40</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>5</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>7</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>170</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>80</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.625</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4997,144 +5357,356 @@
           <t>P11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>15.07.1965</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>University Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Stroke</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>82kg</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2 (right), 0 (left)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>two months</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>28</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>3</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>3</v>
+      </c>
       <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3</v>
+      </c>
       <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>2</v>
+      </c>
       <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>2</v>
+      </c>
       <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>2</v>
+      </c>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3</v>
+      </c>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>3</v>
+      </c>
       <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>2</v>
+      </c>
       <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>3</v>
+      </c>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2</v>
+      </c>
       <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
+      <c r="BJ12" t="n">
+        <v>3</v>
+      </c>
       <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
+      <c r="BL12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2</v>
+      </c>
       <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BP12" t="n">
+        <v>3</v>
+      </c>
       <c r="BQ12" t="inlineStr"/>
-      <c r="BR12" t="inlineStr"/>
-      <c r="BS12" t="inlineStr"/>
-      <c r="BT12" t="inlineStr"/>
-      <c r="BU12" t="inlineStr"/>
-      <c r="BV12" t="inlineStr"/>
-      <c r="BW12" t="inlineStr"/>
-      <c r="BX12" t="inlineStr"/>
-      <c r="BY12" t="inlineStr"/>
-      <c r="BZ12" t="inlineStr"/>
-      <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
-      <c r="CC12" t="inlineStr"/>
+      <c r="BR12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>3</v>
+      </c>
       <c r="CD12" t="inlineStr"/>
-      <c r="CE12" t="inlineStr"/>
+      <c r="CE12" t="n">
+        <v>3</v>
+      </c>
       <c r="CF12" t="inlineStr"/>
-      <c r="CG12" t="inlineStr"/>
+      <c r="CG12" t="n">
+        <v>3</v>
+      </c>
       <c r="CH12" t="inlineStr"/>
-      <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="inlineStr"/>
-      <c r="CK12" t="inlineStr"/>
+      <c r="CI12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>3</v>
+      </c>
       <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
+      <c r="CM12" t="n">
+        <v>3</v>
+      </c>
       <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="inlineStr"/>
+      <c r="CO12" t="n">
+        <v>3</v>
+      </c>
       <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
+      <c r="CQ12" t="n">
+        <v>2</v>
+      </c>
       <c r="CR12" t="inlineStr"/>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
+      <c r="CS12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>3</v>
+      </c>
       <c r="CV12" t="inlineStr"/>
-      <c r="CW12" t="inlineStr"/>
+      <c r="CW12" t="n">
+        <v>3</v>
+      </c>
       <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="inlineStr"/>
+      <c r="CY12" t="n">
+        <v>3</v>
+      </c>
       <c r="CZ12" t="inlineStr"/>
-      <c r="DA12" t="inlineStr"/>
+      <c r="DA12" t="n">
+        <v>1</v>
+      </c>
       <c r="DB12" t="inlineStr"/>
-      <c r="DC12" t="inlineStr"/>
+      <c r="DC12" t="n">
+        <v>3</v>
+      </c>
       <c r="DD12" t="inlineStr"/>
-      <c r="DE12" t="inlineStr"/>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="inlineStr"/>
+      <c r="DE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>6</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>3</v>
+      </c>
       <c r="DH12" t="inlineStr"/>
-      <c r="DI12" t="inlineStr"/>
+      <c r="DI12" t="n">
+        <v>3</v>
+      </c>
       <c r="DJ12" t="inlineStr"/>
-      <c r="DK12" t="inlineStr"/>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
       <c r="DL12" t="inlineStr"/>
-      <c r="DM12" t="inlineStr"/>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
       <c r="DN12" t="inlineStr"/>
-      <c r="DO12" t="inlineStr"/>
-      <c r="DP12" t="inlineStr"/>
-      <c r="DQ12" t="inlineStr"/>
+      <c r="DO12" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>7</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
       <c r="DR12" t="inlineStr"/>
-      <c r="DS12" t="inlineStr"/>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
       <c r="DT12" t="inlineStr"/>
       <c r="DU12" t="inlineStr"/>
       <c r="DV12" t="inlineStr"/>
-      <c r="DW12" t="inlineStr"/>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
       <c r="DX12" t="inlineStr"/>
-      <c r="DY12" t="inlineStr"/>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ12" t="inlineStr"/>
       <c r="EA12" t="inlineStr"/>
       <c r="EB12" t="inlineStr"/>
-      <c r="EC12" t="inlineStr"/>
-      <c r="ED12" t="inlineStr"/>
-      <c r="EE12" t="inlineStr"/>
-      <c r="EF12" t="inlineStr"/>
-      <c r="EG12" t="inlineStr"/>
-      <c r="EH12" t="inlineStr"/>
-      <c r="EI12" t="inlineStr"/>
+      <c r="EC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>6</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>7</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5192,30 +5764,32 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>few weeks</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>30</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>15</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
         <v>3</v>
       </c>
@@ -5226,268 +5800,268 @@
         <v>3</v>
       </c>
       <c r="W13" t="n">
+        <v>15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="n">
         <v>31</v>
       </c>
-      <c r="X13" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>7</v>
-      </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="n">
         <v>16</v>
       </c>
-      <c r="AB13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE13" t="n">
         <v>18</v>
       </c>
-      <c r="AD13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
         <v>5</v>
       </c>
-      <c r="AF13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
         <v>24</v>
       </c>
-      <c r="AH13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" t="n">
         <v>35</v>
       </c>
-      <c r="AL13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO13" t="n">
         <v>51</v>
       </c>
-      <c r="AN13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>261</v>
       </c>
-      <c r="AP13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" t="n">
         <v>63</v>
       </c>
-      <c r="AR13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" t="n">
         <v>123</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AV13" t="n">
         <v>4</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AW13" t="n">
         <v>5</v>
       </c>
-      <c r="AV13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" t="n">
         <v>16</v>
       </c>
-      <c r="AX13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA13" t="n">
         <v>13</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BB13" t="n">
         <v>1</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
         <v>212</v>
       </c>
-      <c r="BB13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE13" t="n">
         <v>86</v>
       </c>
-      <c r="BD13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6</v>
-      </c>
       <c r="BF13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI13" t="n">
         <v>83</v>
       </c>
-      <c r="BH13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI13" t="n">
+      <c r="BJ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK13" t="n">
         <v>48</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>7</v>
-      </c>
       <c r="BL13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BM13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO13" t="n">
         <v>113</v>
       </c>
-      <c r="BN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO13" t="n">
+      <c r="BP13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>84</v>
       </c>
-      <c r="BP13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>7</v>
-      </c>
       <c r="BR13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BS13" t="n">
         <v>7</v>
       </c>
       <c r="BT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV13" t="n">
         <v>5</v>
       </c>
-      <c r="BU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
       <c r="BW13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
         <v>1.923</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="BZ13" t="n">
         <v>2.083</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CA13" t="n">
         <v>2.167</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CB13" t="n">
         <v>1.5</v>
       </c>
-      <c r="CA13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB13" t="n">
+      <c r="CC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD13" t="n">
         <v>15</v>
       </c>
-      <c r="CC13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD13" t="n">
+      <c r="CE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF13" t="n">
         <v>13</v>
       </c>
-      <c r="CE13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CF13" t="n">
+      <c r="CG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH13" t="n">
         <v>19</v>
       </c>
-      <c r="CG13" t="n">
-        <v>7</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>7</v>
-      </c>
       <c r="CI13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CJ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL13" t="n">
         <v>25</v>
       </c>
-      <c r="CK13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CL13" t="n">
+      <c r="CM13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN13" t="n">
         <v>20</v>
       </c>
-      <c r="CM13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN13" t="n">
+      <c r="CO13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP13" t="n">
         <v>9</v>
       </c>
-      <c r="CO13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CP13" t="n">
+      <c r="CQ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR13" t="n">
         <v>24</v>
       </c>
-      <c r="CQ13" t="n">
+      <c r="CS13" t="n">
         <v>5</v>
       </c>
-      <c r="CR13" t="n">
-        <v>6</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>3</v>
-      </c>
       <c r="CT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV13" t="n">
         <v>75</v>
       </c>
-      <c r="CU13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV13" t="n">
+      <c r="CW13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX13" t="n">
         <v>18</v>
       </c>
-      <c r="CW13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CX13" t="n">
+      <c r="CY13" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ13" t="n">
         <v>75</v>
       </c>
-      <c r="CY13" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ13" t="n">
+      <c r="DA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB13" t="n">
         <v>34</v>
       </c>
-      <c r="DA13" t="n">
-        <v>3</v>
-      </c>
-      <c r="DB13" t="n">
+      <c r="DC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD13" t="n">
         <v>102</v>
       </c>
-      <c r="DC13" t="n">
+      <c r="DE13" t="n">
         <v>4</v>
       </c>
-      <c r="DD13" t="n">
-        <v>6</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>3</v>
-      </c>
       <c r="DF13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="DG13" t="n">
         <v>3</v>
@@ -5496,64 +6070,70 @@
         <v>12</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ13" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>12</v>
+      </c>
       <c r="DK13" t="n">
         <v>0</v>
       </c>
       <c r="DL13" t="inlineStr"/>
       <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="n">
         <v>5</v>
       </c>
-      <c r="DN13" t="n">
-        <v>7</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP13" t="inlineStr"/>
+      <c r="DP13" t="n">
+        <v>7</v>
+      </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="inlineStr"/>
-      <c r="DS13" t="inlineStr"/>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
       <c r="DT13" t="inlineStr"/>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
+      <c r="DU13" t="inlineStr"/>
       <c r="DV13" t="inlineStr"/>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="inlineStr"/>
-      <c r="DY13" t="inlineStr"/>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ13" t="inlineStr"/>
-      <c r="EA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="EB13" t="n">
+      <c r="EA13" t="inlineStr"/>
+      <c r="EB13" t="inlineStr"/>
+      <c r="EC13" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED13" t="n">
         <v>4</v>
       </c>
-      <c r="EC13" t="n">
+      <c r="EE13" t="n">
         <v>5</v>
       </c>
-      <c r="ED13" t="n">
-        <v>6</v>
-      </c>
-      <c r="EE13" t="n">
-        <v>0</v>
-      </c>
       <c r="EF13" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH13" t="n">
         <v>1.115</v>
       </c>
-      <c r="EG13" t="n">
+      <c r="EI13" t="n">
         <v>1.417</v>
       </c>
-      <c r="EH13" t="n">
+      <c r="EJ13" t="n">
         <v>1.333</v>
       </c>
-      <c r="EI13" t="n">
+      <c r="EK13" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5701,6 +6281,8 @@
       <c r="EG14" t="inlineStr"/>
       <c r="EH14" t="inlineStr"/>
       <c r="EI14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr"/>
+      <c r="EK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5846,6 +6428,8 @@
       <c r="EG15" t="inlineStr"/>
       <c r="EH15" t="inlineStr"/>
       <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5991,6 +6575,8 @@
       <c r="EG16" t="inlineStr"/>
       <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
+      <c r="EK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6136,6 +6722,8 @@
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr"/>
+      <c r="EJ17" t="inlineStr"/>
+      <c r="EK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6281,6 +6869,8 @@
       <c r="EG18" t="inlineStr"/>
       <c r="EH18" t="inlineStr"/>
       <c r="EI18" t="inlineStr"/>
+      <c r="EJ18" t="inlineStr"/>
+      <c r="EK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6426,6 +7016,8 @@
       <c r="EG19" t="inlineStr"/>
       <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr"/>
+      <c r="EJ19" t="inlineStr"/>
+      <c r="EK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6571,6 +7163,8 @@
       <c r="EG20" t="inlineStr"/>
       <c r="EH20" t="inlineStr"/>
       <c r="EI20" t="inlineStr"/>
+      <c r="EJ20" t="inlineStr"/>
+      <c r="EK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6716,6 +7310,8 @@
       <c r="EG21" t="inlineStr"/>
       <c r="EH21" t="inlineStr"/>
       <c r="EI21" t="inlineStr"/>
+      <c r="EJ21" t="inlineStr"/>
+      <c r="EK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6861,6 +7457,8 @@
       <c r="EG22" t="inlineStr"/>
       <c r="EH22" t="inlineStr"/>
       <c r="EI22" t="inlineStr"/>
+      <c r="EJ22" t="inlineStr"/>
+      <c r="EK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7006,6 +7604,151 @@
       <c r="EG23" t="inlineStr"/>
       <c r="EH23" t="inlineStr"/>
       <c r="EI23" t="inlineStr"/>
+      <c r="EJ23" t="inlineStr"/>
+      <c r="EK23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr"/>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
+      <c r="DD24" t="inlineStr"/>
+      <c r="DE24" t="inlineStr"/>
+      <c r="DF24" t="inlineStr"/>
+      <c r="DG24" t="inlineStr"/>
+      <c r="DH24" t="inlineStr"/>
+      <c r="DI24" t="inlineStr"/>
+      <c r="DJ24" t="inlineStr"/>
+      <c r="DK24" t="inlineStr"/>
+      <c r="DL24" t="inlineStr"/>
+      <c r="DM24" t="inlineStr"/>
+      <c r="DN24" t="inlineStr"/>
+      <c r="DO24" t="inlineStr"/>
+      <c r="DP24" t="inlineStr"/>
+      <c r="DQ24" t="inlineStr"/>
+      <c r="DR24" t="inlineStr"/>
+      <c r="DS24" t="inlineStr"/>
+      <c r="DT24" t="inlineStr"/>
+      <c r="DU24" t="inlineStr"/>
+      <c r="DV24" t="inlineStr"/>
+      <c r="DW24" t="inlineStr"/>
+      <c r="DX24" t="inlineStr"/>
+      <c r="DY24" t="inlineStr"/>
+      <c r="DZ24" t="inlineStr"/>
+      <c r="EA24" t="inlineStr"/>
+      <c r="EB24" t="inlineStr"/>
+      <c r="EC24" t="inlineStr"/>
+      <c r="ED24" t="inlineStr"/>
+      <c r="EE24" t="inlineStr"/>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr"/>
+      <c r="EH24" t="inlineStr"/>
+      <c r="EI24" t="inlineStr"/>
+      <c r="EJ24" t="inlineStr"/>
+      <c r="EK24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/merged_data.xlsx
+++ b/Data/merged_data.xlsx
@@ -5432,15 +5432,21 @@
       <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>19</v>
+      </c>
       <c r="V12" t="n">
         <v>3</v>
       </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>19</v>
+      </c>
       <c r="X12" t="n">
         <v>3</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>35</v>
+      </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
@@ -5450,19 +5456,27 @@
       <c r="AB12" t="n">
         <v>3</v>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>18</v>
+      </c>
       <c r="AD12" t="n">
         <v>3</v>
       </c>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>21</v>
+      </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
-      <c r="AG12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>5</v>
+      </c>
       <c r="AH12" t="n">
         <v>3</v>
       </c>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>30</v>
+      </c>
       <c r="AJ12" t="n">
         <v>7</v>
       </c>
@@ -5472,23 +5486,33 @@
       <c r="AL12" t="n">
         <v>3</v>
       </c>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AM12" t="n">
+        <v>56</v>
+      </c>
       <c r="AN12" t="n">
         <v>1</v>
       </c>
-      <c r="AO12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>225</v>
+      </c>
       <c r="AP12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>111</v>
+      </c>
       <c r="AR12" t="n">
         <v>2</v>
       </c>
-      <c r="AS12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>142</v>
+      </c>
       <c r="AT12" t="n">
         <v>2</v>
       </c>
-      <c r="AU12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>218</v>
+      </c>
       <c r="AV12" t="n">
         <v>5</v>
       </c>
@@ -5498,19 +5522,27 @@
       <c r="AX12" t="n">
         <v>3</v>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>12</v>
+      </c>
       <c r="AZ12" t="n">
         <v>3</v>
       </c>
-      <c r="BA12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>17</v>
+      </c>
       <c r="BB12" t="n">
         <v>2</v>
       </c>
-      <c r="BC12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>180</v>
+      </c>
       <c r="BD12" t="n">
         <v>3</v>
       </c>
-      <c r="BE12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>88</v>
+      </c>
       <c r="BF12" t="n">
         <v>7</v>
       </c>
@@ -5520,11 +5552,15 @@
       <c r="BH12" t="n">
         <v>2</v>
       </c>
-      <c r="BI12" t="inlineStr"/>
+      <c r="BI12" t="n">
+        <v>105</v>
+      </c>
       <c r="BJ12" t="n">
         <v>3</v>
       </c>
-      <c r="BK12" t="inlineStr"/>
+      <c r="BK12" t="n">
+        <v>41</v>
+      </c>
       <c r="BL12" t="n">
         <v>7</v>
       </c>
@@ -5534,11 +5570,15 @@
       <c r="BN12" t="n">
         <v>2</v>
       </c>
-      <c r="BO12" t="inlineStr"/>
+      <c r="BO12" t="n">
+        <v>155</v>
+      </c>
       <c r="BP12" t="n">
         <v>3</v>
       </c>
-      <c r="BQ12" t="inlineStr"/>
+      <c r="BQ12" t="n">
+        <v>74</v>
+      </c>
       <c r="BR12" t="n">
         <v>7</v>
       </c>
@@ -5561,29 +5601,35 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.23</v>
+        <v>2.231</v>
       </c>
       <c r="BZ12" t="n">
         <v>2</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.17</v>
+        <v>2.167</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.63</v>
+        <v>2.625</v>
       </c>
       <c r="CC12" t="n">
         <v>3</v>
       </c>
-      <c r="CD12" t="inlineStr"/>
+      <c r="CD12" t="n">
+        <v>45</v>
+      </c>
       <c r="CE12" t="n">
         <v>3</v>
       </c>
-      <c r="CF12" t="inlineStr"/>
+      <c r="CF12" t="n">
+        <v>16</v>
+      </c>
       <c r="CG12" t="n">
         <v>3</v>
       </c>
-      <c r="CH12" t="inlineStr"/>
+      <c r="CH12" t="n">
+        <v>26</v>
+      </c>
       <c r="CI12" t="n">
         <v>7</v>
       </c>
@@ -5593,19 +5639,27 @@
       <c r="CK12" t="n">
         <v>3</v>
       </c>
-      <c r="CL12" t="inlineStr"/>
+      <c r="CL12" t="n">
+        <v>28</v>
+      </c>
       <c r="CM12" t="n">
         <v>3</v>
       </c>
-      <c r="CN12" t="inlineStr"/>
+      <c r="CN12" t="n">
+        <v>26</v>
+      </c>
       <c r="CO12" t="n">
         <v>3</v>
       </c>
-      <c r="CP12" t="inlineStr"/>
+      <c r="CP12" t="n">
+        <v>7</v>
+      </c>
       <c r="CQ12" t="n">
         <v>2</v>
       </c>
-      <c r="CR12" t="inlineStr"/>
+      <c r="CR12" t="n">
+        <v>51</v>
+      </c>
       <c r="CS12" t="n">
         <v>5</v>
       </c>
@@ -5615,23 +5669,33 @@
       <c r="CU12" t="n">
         <v>3</v>
       </c>
-      <c r="CV12" t="inlineStr"/>
+      <c r="CV12" t="n">
+        <v>54</v>
+      </c>
       <c r="CW12" t="n">
         <v>3</v>
       </c>
-      <c r="CX12" t="inlineStr"/>
+      <c r="CX12" t="n">
+        <v>23</v>
+      </c>
       <c r="CY12" t="n">
         <v>3</v>
       </c>
-      <c r="CZ12" t="inlineStr"/>
+      <c r="CZ12" t="n">
+        <v>149</v>
+      </c>
       <c r="DA12" t="n">
         <v>1</v>
       </c>
-      <c r="DB12" t="inlineStr"/>
+      <c r="DB12" t="n">
+        <v>137</v>
+      </c>
       <c r="DC12" t="n">
-        <v>3</v>
-      </c>
-      <c r="DD12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>60</v>
+      </c>
       <c r="DE12" t="n">
         <v>4</v>
       </c>
@@ -5641,11 +5705,15 @@
       <c r="DG12" t="n">
         <v>3</v>
       </c>
-      <c r="DH12" t="inlineStr"/>
+      <c r="DH12" t="n">
+        <v>8</v>
+      </c>
       <c r="DI12" t="n">
         <v>3</v>
       </c>
-      <c r="DJ12" t="inlineStr"/>
+      <c r="DJ12" t="n">
+        <v>9</v>
+      </c>
       <c r="DK12" t="n">
         <v>0</v>
       </c>
@@ -5696,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="EH12" t="n">
-        <v>1.73</v>
+        <v>1.731</v>
       </c>
       <c r="EI12" t="n">
-        <v>1.83</v>
+        <v>1.833</v>
       </c>
       <c r="EJ12" t="n">
-        <v>1.83</v>
+        <v>1.833</v>
       </c>
       <c r="EK12" t="n">
         <v>1.5</v>
@@ -6143,146 +6211,424 @@
           <t>P13</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>15.04.1977</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>University Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Slip discs, pinched nerves on cervical level</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>78kg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>few weeks</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>27</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="inlineStr"/>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr"/>
-      <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
-      <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="inlineStr"/>
-      <c r="CC14" t="inlineStr"/>
-      <c r="CD14" t="inlineStr"/>
-      <c r="CE14" t="inlineStr"/>
-      <c r="CF14" t="inlineStr"/>
-      <c r="CG14" t="inlineStr"/>
-      <c r="CH14" t="inlineStr"/>
-      <c r="CI14" t="inlineStr"/>
-      <c r="CJ14" t="inlineStr"/>
-      <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="inlineStr"/>
-      <c r="CM14" t="inlineStr"/>
-      <c r="CN14" t="inlineStr"/>
-      <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="inlineStr"/>
-      <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr"/>
-      <c r="CX14" t="inlineStr"/>
-      <c r="CY14" t="inlineStr"/>
-      <c r="CZ14" t="inlineStr"/>
-      <c r="DA14" t="inlineStr"/>
-      <c r="DB14" t="inlineStr"/>
-      <c r="DC14" t="inlineStr"/>
-      <c r="DD14" t="inlineStr"/>
-      <c r="DE14" t="inlineStr"/>
-      <c r="DF14" t="inlineStr"/>
-      <c r="DG14" t="inlineStr"/>
-      <c r="DH14" t="inlineStr"/>
-      <c r="DI14" t="inlineStr"/>
-      <c r="DJ14" t="inlineStr"/>
-      <c r="DK14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>336</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>186</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>166</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>321</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>126</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>77</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>15</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>14</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>7</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>44</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>27</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>10</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>74</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>5</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>51</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>31</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>123</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>121</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>119</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>6</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>12</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
       <c r="DL14" t="inlineStr"/>
-      <c r="DM14" t="inlineStr"/>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
       <c r="DN14" t="inlineStr"/>
-      <c r="DO14" t="inlineStr"/>
-      <c r="DP14" t="inlineStr"/>
-      <c r="DQ14" t="inlineStr"/>
+      <c r="DO14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>4</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
       <c r="DR14" t="inlineStr"/>
-      <c r="DS14" t="inlineStr"/>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
       <c r="DT14" t="inlineStr"/>
       <c r="DU14" t="inlineStr"/>
       <c r="DV14" t="inlineStr"/>
-      <c r="DW14" t="inlineStr"/>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
       <c r="DX14" t="inlineStr"/>
-      <c r="DY14" t="inlineStr"/>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ14" t="inlineStr"/>
       <c r="EA14" t="inlineStr"/>
       <c r="EB14" t="inlineStr"/>
-      <c r="EC14" t="inlineStr"/>
-      <c r="ED14" t="inlineStr"/>
-      <c r="EE14" t="inlineStr"/>
-      <c r="EF14" t="inlineStr"/>
-      <c r="EG14" t="inlineStr"/>
-      <c r="EH14" t="inlineStr"/>
-      <c r="EI14" t="inlineStr"/>
-      <c r="EJ14" t="inlineStr"/>
-      <c r="EK14" t="inlineStr"/>
+      <c r="EC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>5</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6290,13 +6636,33 @@
           <t>P14</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>stroke</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MS (EDSS 1)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -6306,130 +6672,358 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>27</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>24</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>270</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>145</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
       <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
       <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
       <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
       <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
       <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ15" t="inlineStr"/>
       <c r="BR15" t="inlineStr"/>
       <c r="BS15" t="inlineStr"/>
-      <c r="BT15" t="inlineStr"/>
-      <c r="BU15" t="inlineStr"/>
-      <c r="BV15" t="inlineStr"/>
-      <c r="BW15" t="inlineStr"/>
-      <c r="BX15" t="inlineStr"/>
-      <c r="BY15" t="inlineStr"/>
-      <c r="BZ15" t="inlineStr"/>
-      <c r="CA15" t="inlineStr"/>
-      <c r="CB15" t="inlineStr"/>
-      <c r="CC15" t="inlineStr"/>
-      <c r="CD15" t="inlineStr"/>
-      <c r="CE15" t="inlineStr"/>
-      <c r="CF15" t="inlineStr"/>
-      <c r="CG15" t="inlineStr"/>
-      <c r="CH15" t="inlineStr"/>
-      <c r="CI15" t="inlineStr"/>
-      <c r="CJ15" t="inlineStr"/>
-      <c r="CK15" t="inlineStr"/>
-      <c r="CL15" t="inlineStr"/>
-      <c r="CM15" t="inlineStr"/>
-      <c r="CN15" t="inlineStr"/>
-      <c r="CO15" t="inlineStr"/>
-      <c r="CP15" t="inlineStr"/>
-      <c r="CQ15" t="inlineStr"/>
-      <c r="CR15" t="inlineStr"/>
-      <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
-      <c r="CU15" t="inlineStr"/>
-      <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="inlineStr"/>
-      <c r="CX15" t="inlineStr"/>
-      <c r="CY15" t="inlineStr"/>
-      <c r="CZ15" t="inlineStr"/>
-      <c r="DA15" t="inlineStr"/>
-      <c r="DB15" t="inlineStr"/>
-      <c r="DC15" t="inlineStr"/>
-      <c r="DD15" t="inlineStr"/>
-      <c r="DE15" t="inlineStr"/>
-      <c r="DF15" t="inlineStr"/>
-      <c r="DG15" t="inlineStr"/>
-      <c r="DH15" t="inlineStr"/>
-      <c r="DI15" t="inlineStr"/>
-      <c r="DJ15" t="inlineStr"/>
-      <c r="DK15" t="inlineStr"/>
-      <c r="DL15" t="inlineStr"/>
-      <c r="DM15" t="inlineStr"/>
-      <c r="DN15" t="inlineStr"/>
-      <c r="DO15" t="inlineStr"/>
-      <c r="DP15" t="inlineStr"/>
-      <c r="DQ15" t="inlineStr"/>
-      <c r="DR15" t="inlineStr"/>
-      <c r="DS15" t="inlineStr"/>
-      <c r="DT15" t="inlineStr"/>
-      <c r="DU15" t="inlineStr"/>
-      <c r="DV15" t="inlineStr"/>
-      <c r="DW15" t="inlineStr"/>
-      <c r="DX15" t="inlineStr"/>
-      <c r="DY15" t="inlineStr"/>
-      <c r="DZ15" t="inlineStr"/>
-      <c r="EA15" t="inlineStr"/>
-      <c r="EB15" t="inlineStr"/>
-      <c r="EC15" t="inlineStr"/>
-      <c r="ED15" t="inlineStr"/>
-      <c r="EE15" t="inlineStr"/>
-      <c r="EF15" t="inlineStr"/>
-      <c r="EG15" t="inlineStr"/>
-      <c r="EH15" t="inlineStr"/>
-      <c r="EI15" t="inlineStr"/>
-      <c r="EJ15" t="inlineStr"/>
-      <c r="EK15" t="inlineStr"/>
+      <c r="BT15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>50</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>38</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>5</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>24</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>20</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>30</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>5</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>42</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>19</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>228</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>307</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>96</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>4</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>4</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>12</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>306</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>116</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>5</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>304</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>41</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>5</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>5</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>120</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>68</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>5</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>6</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>5</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>4</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6437,14 +7031,42 @@
           <t>P15</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>07.01.1981</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>82kg</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -6455,128 +7077,348 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="inlineStr"/>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr"/>
-      <c r="BR16" t="inlineStr"/>
-      <c r="BS16" t="inlineStr"/>
-      <c r="BT16" t="inlineStr"/>
-      <c r="BU16" t="inlineStr"/>
-      <c r="BV16" t="inlineStr"/>
-      <c r="BW16" t="inlineStr"/>
-      <c r="BX16" t="inlineStr"/>
-      <c r="BY16" t="inlineStr"/>
-      <c r="BZ16" t="inlineStr"/>
-      <c r="CA16" t="inlineStr"/>
-      <c r="CB16" t="inlineStr"/>
-      <c r="CC16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>34</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>73</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>101</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>185</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>82</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>79</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>53</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>103</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>86</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>3</v>
+      </c>
       <c r="CD16" t="inlineStr"/>
-      <c r="CE16" t="inlineStr"/>
-      <c r="CF16" t="inlineStr"/>
-      <c r="CG16" t="inlineStr"/>
-      <c r="CH16" t="inlineStr"/>
-      <c r="CI16" t="inlineStr"/>
-      <c r="CJ16" t="inlineStr"/>
-      <c r="CK16" t="inlineStr"/>
-      <c r="CL16" t="inlineStr"/>
-      <c r="CM16" t="inlineStr"/>
-      <c r="CN16" t="inlineStr"/>
-      <c r="CO16" t="inlineStr"/>
-      <c r="CP16" t="inlineStr"/>
-      <c r="CQ16" t="inlineStr"/>
-      <c r="CR16" t="inlineStr"/>
-      <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
-      <c r="CU16" t="inlineStr"/>
-      <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr"/>
-      <c r="CX16" t="inlineStr"/>
-      <c r="CY16" t="inlineStr"/>
-      <c r="CZ16" t="inlineStr"/>
-      <c r="DA16" t="inlineStr"/>
-      <c r="DB16" t="inlineStr"/>
-      <c r="DC16" t="inlineStr"/>
-      <c r="DD16" t="inlineStr"/>
-      <c r="DE16" t="inlineStr"/>
-      <c r="DF16" t="inlineStr"/>
-      <c r="DG16" t="inlineStr"/>
-      <c r="DH16" t="inlineStr"/>
-      <c r="DI16" t="inlineStr"/>
-      <c r="DJ16" t="inlineStr"/>
-      <c r="DK16" t="inlineStr"/>
+      <c r="CE16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>21</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>13</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>5</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>6</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>22</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>18</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>10</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>42</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>4</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>4</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>35</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>24</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>174</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>65</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>70</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>6</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>12</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
       <c r="DL16" t="inlineStr"/>
-      <c r="DM16" t="inlineStr"/>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
       <c r="DN16" t="inlineStr"/>
-      <c r="DO16" t="inlineStr"/>
-      <c r="DP16" t="inlineStr"/>
-      <c r="DQ16" t="inlineStr"/>
+      <c r="DO16" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>4</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
       <c r="DR16" t="inlineStr"/>
-      <c r="DS16" t="inlineStr"/>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
       <c r="DT16" t="inlineStr"/>
       <c r="DU16" t="inlineStr"/>
       <c r="DV16" t="inlineStr"/>
-      <c r="DW16" t="inlineStr"/>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
       <c r="DX16" t="inlineStr"/>
-      <c r="DY16" t="inlineStr"/>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ16" t="inlineStr"/>
       <c r="EA16" t="inlineStr"/>
       <c r="EB16" t="inlineStr"/>
-      <c r="EC16" t="inlineStr"/>
-      <c r="ED16" t="inlineStr"/>
-      <c r="EE16" t="inlineStr"/>
-      <c r="EF16" t="inlineStr"/>
-      <c r="EG16" t="inlineStr"/>
-      <c r="EH16" t="inlineStr"/>
-      <c r="EI16" t="inlineStr"/>
-      <c r="EJ16" t="inlineStr"/>
-      <c r="EK16" t="inlineStr"/>
+      <c r="EC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>5</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>-0.625</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/Data/merged_data.xlsx
+++ b/Data/merged_data.xlsx
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.10.1957</t>
+          <t>1957-10-15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1186,8 +1186,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1554,7 +1556,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06.05.1963</t>
+          <t>1963-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1587,8 +1589,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>2</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1975,7 +1979,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.04.1969</t>
+          <t>1969-05-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2008,8 +2012,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2404,7 +2410,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29.09.1941</t>
+          <t>1941-09-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2419,7 +2425,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Stroke (ischemic)</t>
+          <t>Stroke</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2437,8 +2443,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>2</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2829,7 +2837,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.08.1948</t>
+          <t>1948-10-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2862,8 +2870,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3246,7 +3256,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.07.1980</t>
+          <t>1980-07-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3279,8 +3289,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -3667,7 +3679,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.09.1959</t>
+          <t>1959-09-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3700,8 +3712,10 @@
           <t>2 (left), 0(right)</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -4096,7 +4110,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.04.1940</t>
+          <t>1940-11-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4129,8 +4143,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -4521,7 +4537,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>09.08.1957</t>
+          <t>1957-09-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4554,8 +4570,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -4946,7 +4964,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.08.1954</t>
+          <t>1954-08-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4979,8 +4997,10 @@
           <t>2 (left), 0 (right)</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -5369,7 +5389,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.07.1965</t>
+          <t>1965-07-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5402,8 +5422,10 @@
           <t>2 (right), 0 (left)</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>2</v>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -5794,7 +5816,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>09.07.1985</t>
+          <t>1985-09-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5827,8 +5849,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -6223,7 +6247,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.04.1977</t>
+          <t>1977-04-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6256,8 +6280,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -6646,16 +6672,24 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1960-03-16</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stroke</t>
+          <t>Stroke</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6663,14 +6697,42 @@
           <t>MS (EDSS 1)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>71kg</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>28</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
@@ -7043,7 +7105,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>07.01.1981</t>
+          <t>1981-07-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7061,21 +7123,53 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>82kg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>29</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
         <v>3</v>
@@ -7426,146 +7520,430 @@
           <t>P16</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1953-08-18</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fachhochschule</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>89kg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>16 years</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>29</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>35</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>106</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>154</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
       <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
       <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
       <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
       <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr"/>
       <c r="BM17" t="inlineStr"/>
-      <c r="BN17" t="inlineStr"/>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
       <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ17" t="inlineStr"/>
       <c r="BR17" t="inlineStr"/>
       <c r="BS17" t="inlineStr"/>
-      <c r="BT17" t="inlineStr"/>
-      <c r="BU17" t="inlineStr"/>
-      <c r="BV17" t="inlineStr"/>
-      <c r="BW17" t="inlineStr"/>
-      <c r="BX17" t="inlineStr"/>
-      <c r="BY17" t="inlineStr"/>
-      <c r="BZ17" t="inlineStr"/>
-      <c r="CA17" t="inlineStr"/>
-      <c r="CB17" t="inlineStr"/>
-      <c r="CC17" t="inlineStr"/>
-      <c r="CD17" t="inlineStr"/>
-      <c r="CE17" t="inlineStr"/>
-      <c r="CF17" t="inlineStr"/>
-      <c r="CG17" t="inlineStr"/>
-      <c r="CH17" t="inlineStr"/>
-      <c r="CI17" t="inlineStr"/>
-      <c r="CJ17" t="inlineStr"/>
-      <c r="CK17" t="inlineStr"/>
-      <c r="CL17" t="inlineStr"/>
-      <c r="CM17" t="inlineStr"/>
-      <c r="CN17" t="inlineStr"/>
-      <c r="CO17" t="inlineStr"/>
-      <c r="CP17" t="inlineStr"/>
-      <c r="CQ17" t="inlineStr"/>
-      <c r="CR17" t="inlineStr"/>
-      <c r="CS17" t="inlineStr"/>
-      <c r="CT17" t="inlineStr"/>
-      <c r="CU17" t="inlineStr"/>
-      <c r="CV17" t="inlineStr"/>
-      <c r="CW17" t="inlineStr"/>
-      <c r="CX17" t="inlineStr"/>
-      <c r="CY17" t="inlineStr"/>
-      <c r="CZ17" t="inlineStr"/>
-      <c r="DA17" t="inlineStr"/>
-      <c r="DB17" t="inlineStr"/>
-      <c r="DC17" t="inlineStr"/>
-      <c r="DD17" t="inlineStr"/>
-      <c r="DE17" t="inlineStr"/>
-      <c r="DF17" t="inlineStr"/>
-      <c r="DG17" t="inlineStr"/>
-      <c r="DH17" t="inlineStr"/>
-      <c r="DI17" t="inlineStr"/>
-      <c r="DJ17" t="inlineStr"/>
-      <c r="DK17" t="inlineStr"/>
-      <c r="DL17" t="inlineStr"/>
-      <c r="DM17" t="inlineStr"/>
-      <c r="DN17" t="inlineStr"/>
-      <c r="DO17" t="inlineStr"/>
-      <c r="DP17" t="inlineStr"/>
-      <c r="DQ17" t="inlineStr"/>
-      <c r="DR17" t="inlineStr"/>
-      <c r="DS17" t="inlineStr"/>
-      <c r="DT17" t="inlineStr"/>
-      <c r="DU17" t="inlineStr"/>
-      <c r="DV17" t="inlineStr"/>
-      <c r="DW17" t="inlineStr"/>
-      <c r="DX17" t="inlineStr"/>
-      <c r="DY17" t="inlineStr"/>
-      <c r="DZ17" t="inlineStr"/>
-      <c r="EA17" t="inlineStr"/>
-      <c r="EB17" t="inlineStr"/>
-      <c r="EC17" t="inlineStr"/>
-      <c r="ED17" t="inlineStr"/>
-      <c r="EE17" t="inlineStr"/>
-      <c r="EF17" t="inlineStr"/>
-      <c r="EG17" t="inlineStr"/>
-      <c r="EH17" t="inlineStr"/>
-      <c r="EI17" t="inlineStr"/>
-      <c r="EJ17" t="inlineStr"/>
-      <c r="EK17" t="inlineStr"/>
+      <c r="BT17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.417</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0.167</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>23</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>30</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>23</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>77</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>72</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>31</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>55</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>95</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>7</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>15</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>117</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>113</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>7</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>88</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>90</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>7</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>145</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>81</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>7</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>7</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7573,146 +7951,430 @@
           <t>P17</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1972-02-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>85kg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>&gt;10 years</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>26</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="inlineStr"/>
-      <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
-      <c r="BQ18" t="inlineStr"/>
-      <c r="BR18" t="inlineStr"/>
-      <c r="BS18" t="inlineStr"/>
-      <c r="BT18" t="inlineStr"/>
-      <c r="BU18" t="inlineStr"/>
-      <c r="BV18" t="inlineStr"/>
-      <c r="BW18" t="inlineStr"/>
-      <c r="BX18" t="inlineStr"/>
-      <c r="BY18" t="inlineStr"/>
-      <c r="BZ18" t="inlineStr"/>
-      <c r="CA18" t="inlineStr"/>
-      <c r="CB18" t="inlineStr"/>
-      <c r="CC18" t="inlineStr"/>
-      <c r="CD18" t="inlineStr"/>
-      <c r="CE18" t="inlineStr"/>
-      <c r="CF18" t="inlineStr"/>
-      <c r="CG18" t="inlineStr"/>
-      <c r="CH18" t="inlineStr"/>
-      <c r="CI18" t="inlineStr"/>
-      <c r="CJ18" t="inlineStr"/>
-      <c r="CK18" t="inlineStr"/>
-      <c r="CL18" t="inlineStr"/>
-      <c r="CM18" t="inlineStr"/>
-      <c r="CN18" t="inlineStr"/>
-      <c r="CO18" t="inlineStr"/>
-      <c r="CP18" t="inlineStr"/>
-      <c r="CQ18" t="inlineStr"/>
-      <c r="CR18" t="inlineStr"/>
-      <c r="CS18" t="inlineStr"/>
-      <c r="CT18" t="inlineStr"/>
-      <c r="CU18" t="inlineStr"/>
-      <c r="CV18" t="inlineStr"/>
-      <c r="CW18" t="inlineStr"/>
-      <c r="CX18" t="inlineStr"/>
-      <c r="CY18" t="inlineStr"/>
-      <c r="CZ18" t="inlineStr"/>
-      <c r="DA18" t="inlineStr"/>
-      <c r="DB18" t="inlineStr"/>
-      <c r="DC18" t="inlineStr"/>
-      <c r="DD18" t="inlineStr"/>
-      <c r="DE18" t="inlineStr"/>
-      <c r="DF18" t="inlineStr"/>
-      <c r="DG18" t="inlineStr"/>
-      <c r="DH18" t="inlineStr"/>
-      <c r="DI18" t="inlineStr"/>
-      <c r="DJ18" t="inlineStr"/>
-      <c r="DK18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>50</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>41</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>41</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>54</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>243</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>71</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>249</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>140</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>109</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>132</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>52</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>265</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>104</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>34</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>35</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>6</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>41</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>32</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>12</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>67</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>5</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>5</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>74</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>20</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>154</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>60</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>63</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>7</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>37</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
       <c r="DL18" t="inlineStr"/>
-      <c r="DM18" t="inlineStr"/>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
       <c r="DN18" t="inlineStr"/>
-      <c r="DO18" t="inlineStr"/>
-      <c r="DP18" t="inlineStr"/>
-      <c r="DQ18" t="inlineStr"/>
+      <c r="DO18" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>6</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>0</v>
+      </c>
       <c r="DR18" t="inlineStr"/>
-      <c r="DS18" t="inlineStr"/>
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
       <c r="DT18" t="inlineStr"/>
       <c r="DU18" t="inlineStr"/>
       <c r="DV18" t="inlineStr"/>
-      <c r="DW18" t="inlineStr"/>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
       <c r="DX18" t="inlineStr"/>
-      <c r="DY18" t="inlineStr"/>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
       <c r="DZ18" t="inlineStr"/>
       <c r="EA18" t="inlineStr"/>
       <c r="EB18" t="inlineStr"/>
-      <c r="EC18" t="inlineStr"/>
-      <c r="ED18" t="inlineStr"/>
-      <c r="EE18" t="inlineStr"/>
-      <c r="EF18" t="inlineStr"/>
-      <c r="EG18" t="inlineStr"/>
-      <c r="EH18" t="inlineStr"/>
-      <c r="EI18" t="inlineStr"/>
-      <c r="EJ18" t="inlineStr"/>
-      <c r="EK18" t="inlineStr"/>
+      <c r="EC18" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>5</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7720,146 +8382,424 @@
           <t>P18</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1980-08-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Apprenticeship</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>84kg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0? --&gt; can walk several km but very very slow and difficultly, some days he cannot walk at all</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>&gt;20 years, seldom usage</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>10 years, not used anymore</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>26</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>17</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>31</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>78</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
       <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
       <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BF19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
       <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
       <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr"/>
       <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
       <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ19" t="inlineStr"/>
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="inlineStr"/>
-      <c r="BT19" t="inlineStr"/>
-      <c r="BU19" t="inlineStr"/>
-      <c r="BV19" t="inlineStr"/>
-      <c r="BW19" t="inlineStr"/>
-      <c r="BX19" t="inlineStr"/>
-      <c r="BY19" t="inlineStr"/>
-      <c r="BZ19" t="inlineStr"/>
-      <c r="CA19" t="inlineStr"/>
-      <c r="CB19" t="inlineStr"/>
-      <c r="CC19" t="inlineStr"/>
-      <c r="CD19" t="inlineStr"/>
-      <c r="CE19" t="inlineStr"/>
-      <c r="CF19" t="inlineStr"/>
-      <c r="CG19" t="inlineStr"/>
-      <c r="CH19" t="inlineStr"/>
-      <c r="CI19" t="inlineStr"/>
-      <c r="CJ19" t="inlineStr"/>
-      <c r="CK19" t="inlineStr"/>
-      <c r="CL19" t="inlineStr"/>
-      <c r="CM19" t="inlineStr"/>
-      <c r="CN19" t="inlineStr"/>
-      <c r="CO19" t="inlineStr"/>
-      <c r="CP19" t="inlineStr"/>
-      <c r="CQ19" t="inlineStr"/>
-      <c r="CR19" t="inlineStr"/>
-      <c r="CS19" t="inlineStr"/>
-      <c r="CT19" t="inlineStr"/>
-      <c r="CU19" t="inlineStr"/>
-      <c r="CV19" t="inlineStr"/>
-      <c r="CW19" t="inlineStr"/>
-      <c r="CX19" t="inlineStr"/>
-      <c r="CY19" t="inlineStr"/>
-      <c r="CZ19" t="inlineStr"/>
-      <c r="DA19" t="inlineStr"/>
-      <c r="DB19" t="inlineStr"/>
-      <c r="DC19" t="inlineStr"/>
-      <c r="DD19" t="inlineStr"/>
-      <c r="DE19" t="inlineStr"/>
-      <c r="DF19" t="inlineStr"/>
-      <c r="DG19" t="inlineStr"/>
-      <c r="DH19" t="inlineStr"/>
-      <c r="DI19" t="inlineStr"/>
-      <c r="DJ19" t="inlineStr"/>
-      <c r="DK19" t="inlineStr"/>
-      <c r="DL19" t="inlineStr"/>
-      <c r="DM19" t="inlineStr"/>
-      <c r="DN19" t="inlineStr"/>
-      <c r="DO19" t="inlineStr"/>
-      <c r="DP19" t="inlineStr"/>
-      <c r="DQ19" t="inlineStr"/>
-      <c r="DR19" t="inlineStr"/>
-      <c r="DS19" t="inlineStr"/>
-      <c r="DT19" t="inlineStr"/>
-      <c r="DU19" t="inlineStr"/>
-      <c r="DV19" t="inlineStr"/>
-      <c r="DW19" t="inlineStr"/>
-      <c r="DX19" t="inlineStr"/>
-      <c r="DY19" t="inlineStr"/>
-      <c r="DZ19" t="inlineStr"/>
-      <c r="EA19" t="inlineStr"/>
-      <c r="EB19" t="inlineStr"/>
-      <c r="EC19" t="inlineStr"/>
-      <c r="ED19" t="inlineStr"/>
-      <c r="EE19" t="inlineStr"/>
-      <c r="EF19" t="inlineStr"/>
-      <c r="EG19" t="inlineStr"/>
-      <c r="EH19" t="inlineStr"/>
-      <c r="EI19" t="inlineStr"/>
-      <c r="EJ19" t="inlineStr"/>
-      <c r="EK19" t="inlineStr"/>
+      <c r="BT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>43</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>22</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>7</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>17</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>9</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>7</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>6</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>59</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>105</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>140</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>96</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>8</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>220</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>80</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>5</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>80</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>2</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>75</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>6</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>104</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>3</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>86</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>6</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>6</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>7</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>7</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>2.731</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7867,7 +8807,11 @@
           <t>P19</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -8014,7 +8958,11 @@
           <t>P20</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -8161,7 +9109,11 @@
           <t>P21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B (A)</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -8308,7 +9260,11 @@
           <t>P22</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
